--- a/data/daily/2026-09/2026-09-18.xlsx
+++ b/data/daily/2026-09/2026-09-18.xlsx
@@ -1195,14 +1195,39 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
+    <ext cx="342900" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>3</row>
+      <rowOff>0</rowOff>
+    </from>
     <ext cx="381000" cy="457200"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="2" name="Image 2" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId2"/>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1217,17 +1242,42 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>3</row>
+      <row>4</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="342900" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>5</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="457200"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="3" name="Image 3" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId3"/>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1242,17 +1292,92 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>4</row>
+      <row>6</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="381000" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>7</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="381000" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>8</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="381000" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>9</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="342900" cy="457200"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="4" name="Image 4" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId4"/>
+        <cNvPr id="9" name="Image 9" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId9"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1267,135 +1392,10 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>5</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="361950" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="5" name="Image 5" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>6</row>
+      <row>10</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="342900" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="6" name="Image 6" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>7</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="323850" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="7" name="Image 7" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>8</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="381000" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="8" name="Image 8" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId8"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>9</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="381000" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="9" name="Image 9" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId9"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>10</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="381000" cy="457200"/>
     <pic>
       <nvPicPr>
         <cNvPr id="10" name="Image 10" descr="Picture"/>
@@ -1450,207 +1450,207 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
+    <ext cx="933450" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
     <ext cx="1028700" cy="1238250"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="2" name="Image 2" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>4</col>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>5</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
+    <ext cx="933450" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
     <ext cx="1028700" cy="1238250"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="3" name="Image 3" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
+    <ext cx="1028700" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1028700" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1028700" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>10</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
     <ext cx="933450" cy="1238250"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="4" name="Image 4" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>6</col>
+        <cNvPr id="9" name="Image 9" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>11</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="990600" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="5" name="Image 5" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>7</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
     <ext cx="933450" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="6" name="Image 6" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>8</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="866775" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="7" name="Image 7" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>9</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1028700" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="8" name="Image 8" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId8"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>10</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1028700" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="9" name="Image 9" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId9"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>11</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1028700" cy="1238250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="10" name="Image 10" descr="Picture"/>
@@ -2600,15 +2600,19 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>알찬 구성과 선물용 패키지 — 추가 보너스 수량과 고급스러운 명절 선물 패키지로 선물용 만족도가 높음</t>
+          <t>알찬 보너스 구성 — 8입 구성에 1개가 추가 보너스로 들어있어 알찬 느낌을 줌</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>간편한 섭취와 빠른 활력 충전 — 액상과 정제를 함께 섭취하는 방식으로 편리하며 빠른 활력 충전에 도움 됨</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr"/>
+          <t>우수한 포장 마감 — 패키지 마감이 튼튼하고 명절 선물용으로 적합한 고급스러운 디자인임</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>빠른 활력 충전 — 복용 후 에너지가 바로 켜지는 듯한 피로 회복 효과를 경험함</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
@@ -2651,21 +2655,21 @@
         <v>4</v>
       </c>
       <c r="J3" t="n">
-        <v>15415</v>
+        <v>15417</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>간편한 올인원 섭취 방식 — 액상과 정제가 함께 있어 물 없이도 깔끔하고 간편하게 섭취 가능함</t>
+          <t>편리한 이중 제형 — 정제와 액상을 함께 먹는 타입으로 물 없이도 간편하게 복용 가능함</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>알찬 추가 구성과 피로 회복 — 10입에 1입 추가 구성으로 알차며 섭취 후 피로감이 줄어 컨디션 유지에 좋음</t>
+          <t>실속 있는 패키지 — 추가 증정 1입이 포함되어 구성이 알차고 선물용으로 좋음</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>고급스러운 선물용 패키지 — 남색 톤의 고급스러운 디자인과 GMP 인증으로 신뢰도가 높아 선물로 적합함</t>
+          <t>피로 회복 효과 — 섭취 후 하루 컨디션이 향상되고 힘이 나는 느낌을 받음</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -2714,21 +2718,25 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>우수한 피로 회복 효과 — 섭취 후 피로가 풀어지고 에너지가 생기며 컨디션 유지에 도움 됨</t>
+          <t>뛰어난 피로 해소 — 바닥난 체력과 피로감을 회복하는 데 실질적인 도움을 줌</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>고급스러운 포장 상태 — 선물용으로 적합하게 포장이 고급스럽고 깔끔하게 도착함</t>
+          <t>고급스러운 포장 — 선물용으로 적합하도록 깔끔하고 품격 있게 포장되어 배송됨</t>
         </is>
       </c>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
-          <t>부담스러운 가격과 가격 변동 — 제품 가격이 다소 비싸고 구매 후 가격 할인이 진행되어 아쉬움</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr"/>
+          <t>부담스러운 가격 — 직접 구매하여 꾸준히 섭취하기에는 다소 가격대가 높음</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>구매 후 가격 변동 — 제품 구매 직후 판매 가격이 만 원 내려가 아쉬움을 느낌</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr"/>
     </row>
     <row r="5" ht="38" customHeight="1">
@@ -2773,15 +2781,19 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>빠른 피로 회복과 활력 증진 — 섭취 후 확실한 피로 감소와 함께 빠른 활력을 체감함</t>
+          <t>즉각적인 에너지 — 섭취 후 밤에 잠을 이루기 힘들 정도로 강한 활력 효과를 체감함</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>간편하고 실용적인 비타민 충전 — 매일 간편하게 비타민을 챙길 수 있어 선물용으로 실용적임</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr"/>
+          <t>간편한 건강 관리 — 하루 한 병으로 비타민과 미네랄을 완전하고 간편하게 챙길 수 있음</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>선물용 적합성 — 포장이 깔끔하고 알차서 주변 지인 응원 및 회복용 선물로 유용함</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
@@ -2824,21 +2836,21 @@
         <v>4</v>
       </c>
       <c r="J6" t="n">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>쉬운 정제 섭취와 편리함 — 정제 크기가 크지 않아 삼키기 쉽고 멀티비타민을 한 번에 챙길 수 있음</t>
+          <t>확실한 컨디션업 — 일상의 육아와 업무 피로에서 빠르게 회복시켜 주는 효과가 있음</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>확실한 컨디션 회복 효과 — 육아나 일상 피로로 지친 몸의 컨디션을 회복하는 데 효과적임</t>
+          <t>삼키기 쉬운 알약 — 액상 위에 얹어진 알약의 크기가 작아 목 넘김이 수월함</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>고급스러운 선물용 패키지 — 포장이 고급스러워 생일이나 기념일 선물용으로 추천함</t>
+          <t>우수한 휴대성 — 가방에 넣어 다니다가 필요할 때 편리하게 먹을 수 있음</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -2887,18 +2899,22 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>맛있고 간편한 구미 제형 — 맛있고 쫄깃하여 챙겨 먹기 귀찮은 영양제를 간식처럼 쉽게 섭취함</t>
+          <t>뛰어난 맛과 식감 — 향긋하고 쫄깃하여 영양제라기보다 맛있는 젤리를 먹는 느낌임</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>귀여운 포장과 합리적 가격 — 패키지 포장이 귀엽고 쿠폰 할인을 통해 저렴하게 구매함</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr"/>
+          <t>간편한 영양 보충 — 귀찮은 영양제 섭취를 간식처럼 매일 잊지 않고 챙길 수 있음</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>상큼한 패키지 — 포장 디자인이 상큼하고 예뻐서 선물 받는 기분을 내기에 좋음</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>체감 효과에 대한 의구심 — 구미 제형 특성상 영양제로서의 명확한 효과 체감이 다소 부족함</t>
+          <t>섭취량 제한 아쉬움 — 맛이 좋아서 더 먹고 싶으나 하루 권장량이 2개로 한정되어 아쉬움</t>
         </is>
       </c>
       <c r="O7" t="inlineStr"/>
@@ -2942,29 +2958,29 @@
         <v>4</v>
       </c>
       <c r="J8" t="n">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>체감되는 피로 회복 효과 — 섭취 유무에 따른 차이가 크고 운동이나 야근 후 피로 회복에 도움 됨</t>
+          <t>빠른 체력 회복 — 운동 후 피로하거나 갱년기 기력 저하 시 즉각적으로 컨디션이 회복됨</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>부담 없는 정제 크기와 맛 — 알약 크기가 작고 액상의 신맛이과하지 않아 위가 약해도 먹기 수월함</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>넉넉한 용량과 사은품 증정 — 대용량 구성에 레몬샷 등 증정품이 동봉되어 알참</t>
-        </is>
-      </c>
+          <t>풍성한 증정 혜택 — 대용량 본품에 레몬샷 사은품까지 함께 증정되어 혜택이 좋음</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
-          <t>배송 지연 및 박스 파손 — 배송이 늦어지거나 포장 박스가 찢어져서도착함</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr"/>
+          <t>배송 지연 발생 — 주문 후 상품 배송이 다소 늦어지는 불편함이 있었음</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>포장 박스 파손 — 배송 과정 중 외부 포장 박스가 일부 찢어진 상태로 도착함</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr"/>
     </row>
     <row r="9" ht="38" customHeight="1">
@@ -3009,17 +3025,17 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>높은 신뢰와 고급 포장 — 정관장 브랜드 신뢰도가 높고 용기와 패키지가 고급스러움</t>
+          <t>독특한 복용 방식 — 알약 형태가 아닌 분말과 액상을 섞어서 상큼달콤하게 마시는 방식임</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>간편하고 맛있는 섭취 방식 — 액상과 분말을 섞어 먹는 방식이 이색적이며 달콤새콤해서 먹기 편함</t>
+          <t>높은 브랜드 신뢰 — 정관장 브랜드 제품이라 안심하고 섭취하며 선물용으로도 신뢰가 감</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>추가 증정 및 피로 개선 — 증정 1입이 포함된 알찬 구성이며 피곤함 완화에 효과가 있음</t>
+          <t>고급 용기 패키지 — 빈 병을 버리기 아까울 정도로 용기와 포장 디자인이 고급스러움</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -3068,17 +3084,17 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>우수한 피로 회복 효과 — 섭취 후 피로가 풀리고 하루를 개운하고 활력 있게 보낼 수 있음</t>
+          <t>강력한 활력 증진 — 피로 해소 효과가 뛰어나며 복용 후 몸에 가득한 활력을 느끼게 됨</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>좋은 맛과 간편한 휴대성 — 작은 병 형태로 들고 다니기 좋으며 맛도 있어서 섭취가 즐거움</t>
+          <t>간편한 이중 제형 — 작은 병 하나에 음료와 정제가 같이 들어 있어 간편하게 먹기 좋음</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>선물용으로 우수한 디자인 — 패키지가 깜찍하고 고급스러워 응원이나 명절 선물로 받았을 때 기분이 좋음</t>
+          <t>센스 있는 구성품 — 추석 맞춤 패키지에 추가 비타민 젤리까지 포함되어 풍성함</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -3116,28 +3132,28 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260907140842_cd1cc97e88614bab990f40725f7f84c6.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260918101845_2aa1c2f10c9e4652af1df550ad2cc225.jpg</t>
         </is>
       </c>
       <c r="I11" t="n">
         <v>4</v>
       </c>
       <c r="J11" t="n">
-        <v>29537</v>
+        <v>29538</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>편리한 액상 타입과 달콤한 맛 — 물 없이 간편히 먹는 액상 형태이며 달콤하여 거부감 없이 섭취함</t>
+          <t>편리한 액상 타입 — 물을 따로 챙길 필요 없이 언제 어디서나 바로 섭취할 수 있어 유용함</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>고급 포장과 젤리 증정 — 종이가방이 포함된 깔끔한 포장에 맛있는 비타민 젤리가 사은품으로 제공됨</t>
+          <t>호불호 없는 맛 — 비타민 특유의 역한 맛이 전혀 없고 깔끔하고 달콤하여 먹기 편함</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>피로 회복과 컨디션 개선 — 야근이나 시험 기간 등 지칠 때 마시면 컨디션 회복에 도움 됨</t>
+          <t>고급스러운 포장 — 종이가방이 함께 동봉되어 명절이나 축하 선물용으로 품격이 있음</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -3155,7 +3171,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>[그레인온] 골드 카무트 브랜드밀 효소 3개월(+선물포장) +파로효소 그린캡슐레이션 증정</t>
+          <t>[리센느에디션] 베리말차 캡슐레이션 효소 1.8g 30포, 2개</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -3165,52 +3181,56 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>43,900원</t>
+          <t>24,900원</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/13180343</t>
+          <t>https://gift.kakao.com/product/14208051</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260915132146_bf977745343b4bb485cda5b48cdc1dd2.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260908134122_cb4724fa4d2d4e45b370faede2a463a5.jpg</t>
         </is>
       </c>
       <c r="I12" t="n">
         <v>4</v>
       </c>
       <c r="J12" t="n">
-        <v>1666</v>
+        <v>88</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>소화 개선 및 변비 완화 — 식후 소화 불량 해소에 도움을 주며 변비 증상이 좋아짐</t>
+          <t>매력적인 굿즈 — 모델 리센느 원이의 포토카드와 사은품이 포함되어 팬들의 만족도가 높음</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>저렴한 가격과 덤 구성 — 가격이 착하고 파로효소 추가 증정 등 사은품 구성이 훌륭함</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>고급스러운 선물 포장 — 선물용 포장이 깔끔하고 고급스러워 만족도가 높음</t>
-        </is>
-      </c>
+          <t>맛있는 효소 섭취 — 평소 말차를 잘 못 먹는 사람도 거부감 없이 맛있게 먹을 수 있음</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
-          <t>구매 수량 제한의 아쉬움 — 1인당 구매 제한 갯수가 설정되어 있어 여러 명에게 선물하기에 수량이 모자람</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr"/>
-      <c r="P12" t="inlineStr"/>
+          <t>사은품 수량 오류 — 포토카드 두 장 제공 안내와 달리 실제로는 한 장만 동봉되어 배송됨</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>불만족스러운 배송 — 배송 상태가 단정치 못하고 엉망으로 옴</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>포토카드 고정형 — 포토카드가 랜덤 구성이 아닌 고정형 제품이라 아쉬움</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="38" customHeight="1">
       <c r="B13" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>피부/미용</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -3218,62 +3238,58 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>[리센느에디션] 베리말차 캡슐레이션 효소 1.8g 30포, 2개</t>
+          <t>'3입 증정' "선물하기 1등 콜라겐" 아일로 타입1 콜라겐 비오틴 앰플 28일분 오간자 에디션+ 앰플 3입 추가 증정</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>그레인온</t>
+          <t>아일로</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>24,900원</t>
+          <t>65,900원</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/14208051</t>
+          <t>https://gift.kakao.com/product/4965835</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260908134122_cb4724fa4d2d4e45b370faede2a463a5.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260907091018_68a44d5ed50249e7aa6ad05f30d0e480.jpg</t>
         </is>
       </c>
       <c r="I13" t="n">
         <v>4</v>
       </c>
       <c r="J13" t="n">
-        <v>88</v>
+        <v>734</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>아이돌 굿즈와 풍성한 증정 — 리센느 원이 포토카드와 단백질 스낵 사은품이 동봉되어 구성이 혜자스러움</t>
+          <t>정성 가득한 패키지 — 오간자 에디션의 고급스럽고 은은한 분홍빛 포장이 받는 사람을 기쁘게 함</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>맛있는 맛과 간편함 — 말차를 잘 못 먹는 사람도 맛있게 즐길 수 있는 맛이며 먹기 편함</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>포토카드 구성 불일치 — 안내와 달리 포토카드가 1장만 들어있거나 고정 수령이라 아쉬움</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>배송 상태 불만족 — 제품 품질은 좋으나 배송 과정 및 처리가 불만족스러움</t>
-        </is>
-      </c>
+          <t>풍부한 추가 증정 — 무료 체험 앰플 및 추가 샘플이 들어 있어 구성이 더욱 풍부함</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>피부 맑음 효과 — 꾸준히 마시면 피부가 한결 맑아지고 탱탱해지는 기분을 느낄 수 있음</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr"/>
     </row>
     <row r="14" ht="38" customHeight="1">
       <c r="B14" t="inlineStr">
         <is>
-          <t>피부/미용</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -3281,51 +3297,55 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>'3입 증정' "선물하기 1등 콜라겐" 아일로 타입1 콜라겐 비오틴 앰플 28일분 오간자 에디션+ 앰플 3입 추가 증정</t>
+          <t>[그레인온] 골드 카무트 브랜드밀 효소 3개월(+선물포장) +파로효소 그린캡슐레이션 증정</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>아일로</t>
+          <t>그레인온</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>65,900원</t>
+          <t>43,900원</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/4965835</t>
+          <t>https://gift.kakao.com/product/13180343</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260907091018_68a44d5ed50249e7aa6ad05f30d0e480.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260915132146_bf977745343b4bb485cda5b48cdc1dd2.jpg</t>
         </is>
       </c>
       <c r="I14" t="n">
         <v>4</v>
       </c>
       <c r="J14" t="n">
-        <v>734</v>
+        <v>1666</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>예쁘고 고급스러운 포장 — 정성스럽고 은은한 고급 핑크 포장으로 선물 받는 사람의 기분을 좋게 함</t>
+          <t>원활한 배변 활동 — 폐경 이후 겪은 소화 불량과 만성 변비 증상이 섭취 후 많이 개선됨</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>피부 개선 체감 효과 — 꾸준히 섭취 시 피부가 탱탱해지고 맑아지는 느낌을 받음</t>
+          <t>풍성한 추가 구성 — 파로효소 그린캡슐레이션 등 다양한 덤과 풍성한 사은품이 제공됨</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>섭취 편의성과 앰플 증정 — 마시기 편리한 용기 구조이며 추가 증정 앰플이 포함되어 만족스러움</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
+          <t>착한 세일 가격 — 정가 대비 톡딜 할인 혜택으로 저렴하고 합리적인 가격에 구매함</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>구매 수량 제한 — 한 번에 구매할 수 있는 수량이 한정되어 다수에게 선물하기 불편함</t>
+        </is>
+      </c>
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr"/>
     </row>
@@ -3371,22 +3391,22 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>속 편한 소화 개선 효과 — 식후 복용 시 소화가 잘 되며 소화력이 떨어진 사람에게 효과적임</t>
+          <t>우수한 소화 개선 — 식후 복용 시 소화가 잘되며 나이 들어 저하된 소화력 보완에 효과적임</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>우수한 가성비와 맛 — 맛이 좋고 저렴한 가격에 구매하여 쟁여두고 먹기 좋음</t>
+          <t>높은 가성비 — 총 100포 구성에 파로저당씬칩까지 주면서 가격도 저렴해 실속 있음</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>풍성한 과자 사은품 증정 — 10포 추가 증정 외에도 파로저당씬칩 과자 선물이 제공됨</t>
+          <t>부담 없는 맛 — 효소 특유의 거부감 없이 고소하고 맛이 좋아 간식처럼 섭취함</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>구매 갯수 제한의 아쉬움 — 지인 선물용으로 다량 구매 시 2개 수량 제한이 걸려 있어 아쉬움</t>
+          <t>구매 개수 제한 — 선물용으로 여러 개 사고 싶으나 수량 제한이 걸려 있어 불편함</t>
         </is>
       </c>
       <c r="O15" t="inlineStr"/>
@@ -3434,23 +3454,27 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>다양한 구성과 골라먹는 재미 — 한 달 식단으로 다양한 맛이 들어있어 매일 골라 먹기 좋음</t>
+          <t>훌륭한 가성비 — 30팩이라는 넉넉한 수량을 저렴한 균일 패키지 가격에 획득 가능함</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>착한 가격과 보냉백 증정 — 가격 대비 양이 넉넉하며 도시락용으로 유용한 보냉파우치가 함께 옴</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr"/>
+          <t>다양한 구성 — 여러 가지 맛이 섞여 있어 질리지 않고 매일 골라 먹는 재미가 있음</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>유용한 보냉 가방 — 사은품으로 제공된 보냉백이 실용적이라 도시락용 가방으로 활용하기 좋음</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>포장 터짐 및 소스 누출 — 진공 포장이 헐렁하거나 제품이 터져 주변에 소스가 묻어옴</t>
+          <t>일부 포장 터짐 — 밀봉이 헐렁하게 포장되어 배송 중 제품 일부가 터져 소스가 흘러나옴</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>배송 중 해동 발생 — 배송 시 냉동 상태가 제대로 유지되지 않고 녹아서 도착함</t>
+          <t>제품 해동 배송 — 도착했을 때 냉동 상태가 풀려 닭가슴살이 많이 녹은 채로 수령함</t>
         </is>
       </c>
       <c r="P16" t="inlineStr"/>
@@ -3497,18 +3521,22 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>부드러운 식감과 다양한 맛 — 뻑뻑함이 적고 양념이 맛있으며 구성이 다양해 질리지 않고 섭취함</t>
+          <t>부드러운 식감 — 닭가슴살 특유의 뻑뻑함이 덜하고 매우 촉촉하고 부드러움</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>뛰어난 가성비와 조리 편의성 — 저렴한 가격에 넉넉한 갯수를 제공하며 전자레인지로 간편 조리가 가능함</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr"/>
+          <t>물리지 않는 맛 — 단조롭지 않고 자극적이지 않은 다양한 양념 구성으로 지속 섭취 가능함</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>초특가 세트 — 24팩에 달하는 많은 양의 닭가슴살을 3만 원 이하로 저렴하게 구매함</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>배송 시 제품 해동 문제 — 배송 도착 상태에서 닭가슴살 제품이 전부 녹아서 도착함</t>
+          <t>배송 중 해동됨 — 완전 냉동 상태가 유지되지 않고 배송 과정에서 전부 녹아서 도착함</t>
         </is>
       </c>
       <c r="O17" t="inlineStr"/>
@@ -3556,17 +3584,17 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>비린 맛 없는 부드러운 맛 — 단백질 특유의 비리거나 텁텁한 맛이 없고 일반 우유처럼 맛있음</t>
+          <t>깔끔하고 맛있는 맛 — 단백질 음료 특유의 비리고 텁텁한 맛없이 진하고 달콤함</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>포만감과 편안한 속 — 운동 후 허기를 달래주며 마신 뒤에도 더부룩함 없이 속이 편함</t>
+          <t>포만감 및 영양 — 속을 더부룩하지 않게 하면서도 어느 정도 허기를 달래 주고 영양이 충분함</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>슬림한 용기의 높은 휴대성 — 패키지가 슬림하여 가방에 넣고 다니며 간편하게 챙겨 마시기 좋음</t>
+          <t>슬림한 디자인 — 패키지가 슬림하여 가방에 휴대하여 언제 어디서든 꺼내 먹기 용이함</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -3615,21 +3643,25 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>예쁜 케이스 디자인 — 케이스와 포장이 예뻐서 선물받을 때 만족감이 큼</t>
+          <t>공주풍 예쁜 케이스 — 핑크빛 앰플 병과 외부 패키지가 공주 소품처럼 예뻐서 선물로 가치가 높음</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>부담 없는 맛과 편의성 — 마시기 편리한 앰플 형태이며 비타민 음료 같은 맛으로 부담 없음</t>
+          <t>새콤하고 편한 섭취 — 비타 음료와 비슷한 새콤달콤한 맛이라 물 없이 앰플로 가볍게 복용함</t>
         </is>
       </c>
       <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr">
         <is>
-          <t>진한 농도와 즉각적 효과 미흡 — 마시기에 맛이 다소 진하여 물이 필요하고 단기 섭취 시 효과 체감이 적음</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr"/>
+          <t>다소 강한 맛과 향 — 마실 때 맛이 다소 진하고 목 넘김 후 강해 물을 곁들여 마셔야 함</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>미미한 초기 효과 — 단기간 섭취 기준으로는 눈에 띄는 즉각적인 변화가 잘 보이지 않음</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr"/>
     </row>
     <row r="20" ht="38" customHeight="1">
@@ -3643,7 +3675,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>아메리카노 증정 에너지 활력선물 [김종국 추천세트]익스트림 아르기닌정 (2개월분) &amp; 밀크씨슬 플러스 (2개월분) + 쇼핑백 증정</t>
+          <t>아르기닌 증정 남친 활력선물 대한민국 NO.1 김종국 트리플아르기닌 6200 (30포) + 아르기닌 추가 증정</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -3653,38 +3685,38 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>25,900원</t>
+          <t>43,900원</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/7556791</t>
+          <t>https://gift.kakao.com/product/7417420</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260904160657_c66395adeecf4b11a3a2afd7f4e2d479.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260706153340_3e124da6e254462d9a7efad2521e3b9e.jpg</t>
         </is>
       </c>
       <c r="I20" t="n">
         <v>4</v>
       </c>
       <c r="J20" t="n">
-        <v>1534</v>
+        <v>248</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>확실한 피로 회복 효과 — 아침에 일어날 때 몸이 가벼워지고 일상 피로 완화에 도움 됨</t>
+          <t>검증된 초고함량 — 1포당 L-아르기닌 6,200mg을 함유하여 운동 지구력과 기력 향상에 효과적임</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>운동 집중도 및 활력 향상 — 운동 전에 챙겨 먹으면 쉽게 지치지 않고 운동 수행 능력에 도움이 됨</t>
+          <t>휴대성 좋은 포장 — 개별 스틱 포장으로 설계되어 언제든 챙겨 다니며 먹기 쉬움</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>알찬 세트 구성과 쇼핑백 — 아르기닌과 밀크씨슬 2개월분 구성에 쇼핑백이 포함되어 선물용으로 최고임</t>
+          <t>센스 있는 부속품 — 전용 쇼핑백과 여유분의 아르기닌 스틱이 추가 동봉되어 선물하기에 적절함</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -3702,46 +3734,50 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>"이게 바로 찐! 초고함량" 액상스틱 L-아르기닌 7000 3박스 [케이스 동봉]</t>
+          <t>아메리카노 증정 에너지 활력선물 [김종국 추천세트]익스트림 아르기닌정 (2개월분) &amp; 밀크씨슬 플러스 (2개월분) + 쇼핑백 증정</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>뉴트리디데이</t>
+          <t>익스트림</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>30,900원</t>
+          <t>25,900원</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/4487367</t>
+          <t>https://gift.kakao.com/product/7556791</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260727151443_bd470867f85f4a79857e43d8b82ff835.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260904160657_c66395adeecf4b11a3a2afd7f4e2d479.jpg</t>
         </is>
       </c>
       <c r="I21" t="n">
         <v>4</v>
       </c>
       <c r="J21" t="n">
-        <v>39</v>
+        <v>1534</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>상큼한 레몬 맛과 간편 섭취 — 액상 타입이라 물에 타 먹기 편하고 레몬 맛이라 거부감이 없음</t>
+          <t>활력 있는 아침 — 섭취 후 아침 기상 시 몸이 한결 가볍고 일상생활의 피로가 줄어듦</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>우수한 휴대성과 활력 증진 — 스틱 제형으로 외출 시 챙기기 쉽고 아침 공복이나 운동 전 활력 충전에 좋음</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr"/>
+          <t>이상적인 성분 조화 — 간 건강을 돕는 밀크씨슬과 활력 충전을 주는 아르기닌을 함께 챙길 수 있음</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>2개월의 넉넉한 양 — 2개월분 구성으로 오랜 기간 넉넉하게 본인의 건강을 관리하기 좋음</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr"/>
@@ -4067,7 +4103,7 @@
         <v>16075</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>15415</v>
+        <v>15417</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>3352</v>
@@ -4076,13 +4112,13 @@
         <v>8706</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="H7" s="3" t="n">
         <v>6471</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="J7" s="3" t="n">
         <v>1647</v>
@@ -4091,7 +4127,7 @@
         <v>2619</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>29537</v>
+        <v>29538</v>
       </c>
     </row>
     <row r="8" ht="90" customHeight="1">
@@ -4102,72 +4138,74 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>알찬 구성과 선물용 패키지 — 추가 보너스 수량과 고급스러운 명절 선물 패키지로 선물용 만족도가 높음
-간편한 섭취와 빠른 활력 충전 — 액상과 정제를 함께 섭취하는 방식으로 편리하며 빠른 활력 충전에 도움 됨</t>
+          <t>알찬 보너스 구성 — 8입 구성에 1개가 추가 보너스로 들어있어 알찬 느낌을 줌
+우수한 포장 마감 — 패키지 마감이 튼튼하고 명절 선물용으로 적합한 고급스러운 디자인임
+빠른 활력 충전 — 복용 후 에너지가 바로 켜지는 듯한 피로 회복 효과를 경험함</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>간편한 올인원 섭취 방식 — 액상과 정제가 함께 있어 물 없이도 깔끔하고 간편하게 섭취 가능함
-알찬 추가 구성과 피로 회복 — 10입에 1입 추가 구성으로 알차며 섭취 후 피로감이 줄어 컨디션 유지에 좋음
-고급스러운 선물용 패키지 — 남색 톤의 고급스러운 디자인과 GMP 인증으로 신뢰도가 높아 선물로 적합함</t>
+          <t>편리한 이중 제형 — 정제와 액상을 함께 먹는 타입으로 물 없이도 간편하게 복용 가능함
+실속 있는 패키지 — 추가 증정 1입이 포함되어 구성이 알차고 선물용으로 좋음
+피로 회복 효과 — 섭취 후 하루 컨디션이 향상되고 힘이 나는 느낌을 받음</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>우수한 피로 회복 효과 — 섭취 후 피로가 풀어지고 에너지가 생기며 컨디션 유지에 도움 됨
-고급스러운 포장 상태 — 선물용으로 적합하게 포장이 고급스럽고 깔끔하게 도착함</t>
+          <t>뛰어난 피로 해소 — 바닥난 체력과 피로감을 회복하는 데 실질적인 도움을 줌
+고급스러운 포장 — 선물용으로 적합하도록 깔끔하고 품격 있게 포장되어 배송됨</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>빠른 피로 회복과 활력 증진 — 섭취 후 확실한 피로 감소와 함께 빠른 활력을 체감함
-간편하고 실용적인 비타민 충전 — 매일 간편하게 비타민을 챙길 수 있어 선물용으로 실용적임</t>
+          <t>즉각적인 에너지 — 섭취 후 밤에 잠을 이루기 힘들 정도로 강한 활력 효과를 체감함
+간편한 건강 관리 — 하루 한 병으로 비타민과 미네랄을 완전하고 간편하게 챙길 수 있음
+선물용 적합성 — 포장이 깔끔하고 알차서 주변 지인 응원 및 회복용 선물로 유용함</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>쉬운 정제 섭취와 편리함 — 정제 크기가 크지 않아 삼키기 쉽고 멀티비타민을 한 번에 챙길 수 있음
-확실한 컨디션 회복 효과 — 육아나 일상 피로로 지친 몸의 컨디션을 회복하는 데 효과적임
-고급스러운 선물용 패키지 — 포장이 고급스러워 생일이나 기념일 선물용으로 추천함</t>
+          <t>확실한 컨디션업 — 일상의 육아와 업무 피로에서 빠르게 회복시켜 주는 효과가 있음
+삼키기 쉬운 알약 — 액상 위에 얹어진 알약의 크기가 작아 목 넘김이 수월함
+우수한 휴대성 — 가방에 넣어 다니다가 필요할 때 편리하게 먹을 수 있음</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>맛있고 간편한 구미 제형 — 맛있고 쫄깃하여 챙겨 먹기 귀찮은 영양제를 간식처럼 쉽게 섭취함
-귀여운 포장과 합리적 가격 — 패키지 포장이 귀엽고 쿠폰 할인을 통해 저렴하게 구매함</t>
+          <t>뛰어난 맛과 식감 — 향긋하고 쫄깃하여 영양제라기보다 맛있는 젤리를 먹는 느낌임
+간편한 영양 보충 — 귀찮은 영양제 섭취를 간식처럼 매일 잊지 않고 챙길 수 있음
+상큼한 패키지 — 포장 디자인이 상큼하고 예뻐서 선물 받는 기분을 내기에 좋음</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>체감되는 피로 회복 효과 — 섭취 유무에 따른 차이가 크고 운동이나 야근 후 피로 회복에 도움 됨
-부담 없는 정제 크기와 맛 — 알약 크기가 작고 액상의 신맛이과하지 않아 위가 약해도 먹기 수월함
-넉넉한 용량과 사은품 증정 — 대용량 구성에 레몬샷 등 증정품이 동봉되어 알참</t>
+          <t>빠른 체력 회복 — 운동 후 피로하거나 갱년기 기력 저하 시 즉각적으로 컨디션이 회복됨
+풍성한 증정 혜택 — 대용량 본품에 레몬샷 사은품까지 함께 증정되어 혜택이 좋음</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>높은 신뢰와 고급 포장 — 정관장 브랜드 신뢰도가 높고 용기와 패키지가 고급스러움
-간편하고 맛있는 섭취 방식 — 액상과 분말을 섞어 먹는 방식이 이색적이며 달콤새콤해서 먹기 편함
-추가 증정 및 피로 개선 — 증정 1입이 포함된 알찬 구성이며 피곤함 완화에 효과가 있음</t>
+          <t>독특한 복용 방식 — 알약 형태가 아닌 분말과 액상을 섞어서 상큼달콤하게 마시는 방식임
+높은 브랜드 신뢰 — 정관장 브랜드 제품이라 안심하고 섭취하며 선물용으로도 신뢰가 감
+고급 용기 패키지 — 빈 병을 버리기 아까울 정도로 용기와 포장 디자인이 고급스러움</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>우수한 피로 회복 효과 — 섭취 후 피로가 풀리고 하루를 개운하고 활력 있게 보낼 수 있음
-좋은 맛과 간편한 휴대성 — 작은 병 형태로 들고 다니기 좋으며 맛도 있어서 섭취가 즐거움
-선물용으로 우수한 디자인 — 패키지가 깜찍하고 고급스러워 응원이나 명절 선물로 받았을 때 기분이 좋음</t>
+          <t>강력한 활력 증진 — 피로 해소 효과가 뛰어나며 복용 후 몸에 가득한 활력을 느끼게 됨
+간편한 이중 제형 — 작은 병 하나에 음료와 정제가 같이 들어 있어 간편하게 먹기 좋음
+센스 있는 구성품 — 추석 맞춤 패키지에 추가 비타민 젤리까지 포함되어 풍성함</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>편리한 액상 타입과 달콤한 맛 — 물 없이 간편히 먹는 액상 형태이며 달콤하여 거부감 없이 섭취함
-고급 포장과 젤리 증정 — 종이가방이 포함된 깔끔한 포장에 맛있는 비타민 젤리가 사은품으로 제공됨
-피로 회복과 컨디션 개선 — 야근이나 시험 기간 등 지칠 때 마시면 컨디션 회복에 도움 됨</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
+          <t>편리한 액상 타입 — 물을 따로 챙길 필요 없이 언제 어디서나 바로 섭취할 수 있어 유용함
+호불호 없는 맛 — 비타민 특유의 역한 맛이 전혀 없고 깔끔하고 달콤하여 먹기 편함
+고급스러운 포장 — 종이가방이 함께 동봉되어 명절이나 축하 선물용으로 품격이 있음</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="60" customHeight="1">
       <c r="B9" s="1" t="inlineStr">
         <is>
           <t>부정리뷰</t>
@@ -4177,19 +4215,21 @@
       <c r="D9" s="3" t="inlineStr"/>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>부담스러운 가격과 가격 변동 — 제품 가격이 다소 비싸고 구매 후 가격 할인이 진행되어 아쉬움</t>
+          <t>부담스러운 가격 — 직접 구매하여 꾸준히 섭취하기에는 다소 가격대가 높음
+구매 후 가격 변동 — 제품 구매 직후 판매 가격이 만 원 내려가 아쉬움을 느낌</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr"/>
       <c r="G9" s="3" t="inlineStr"/>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>체감 효과에 대한 의구심 — 구미 제형 특성상 영양제로서의 명확한 효과 체감이 다소 부족함</t>
+          <t>섭취량 제한 아쉬움 — 맛이 좋아서 더 먹고 싶으나 하루 권장량이 2개로 한정되어 아쉬움</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>배송 지연 및 박스 파손 — 배송이 늦어지거나 포장 박스가 찢어져서도착함</t>
+          <t>배송 지연 발생 — 주문 후 상품 배송이 다소 늦어지는 불편함이 있었음
+포장 박스 파손 — 배송 과정 중 외부 포장 박스가 일부 찢어진 상태로 도착함</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr"/>
@@ -4397,12 +4437,12 @@
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
+          <t>피부/미용</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
           <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="E15" s="3" t="inlineStr">
-        <is>
-          <t>피부/미용</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
@@ -4454,39 +4494,39 @@
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
+          <t>아일로</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
           <t>그레인온</t>
         </is>
       </c>
-      <c r="E16" s="3" t="inlineStr">
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>그레인온</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr">
+        <is>
+          <t>한끼통살</t>
+        </is>
+      </c>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>한끼통살</t>
+        </is>
+      </c>
+      <c r="I16" s="3" t="inlineStr">
+        <is>
+          <t>셀렉스</t>
+        </is>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
         <is>
           <t>아일로</t>
         </is>
       </c>
-      <c r="F16" s="3" t="inlineStr">
-        <is>
-          <t>그레인온</t>
-        </is>
-      </c>
-      <c r="G16" s="3" t="inlineStr">
-        <is>
-          <t>한끼통살</t>
-        </is>
-      </c>
-      <c r="H16" s="3" t="inlineStr">
-        <is>
-          <t>한끼통살</t>
-        </is>
-      </c>
-      <c r="I16" s="3" t="inlineStr">
-        <is>
-          <t>셀렉스</t>
-        </is>
-      </c>
-      <c r="J16" s="3" t="inlineStr">
-        <is>
-          <t>아일로</t>
-        </is>
-      </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
           <t>익스트림</t>
@@ -4494,7 +4534,7 @@
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>뉴트리디데이</t>
+          <t>익스트림</t>
         </is>
       </c>
     </row>
@@ -4506,19 +4546,19 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
+          <t>[리센느에디션] 베리말차 캡슐레이션 효소 1.8g 30포, 2개</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>'3입 증정' "선물하기 1등 콜라겐" 아일로 타입1 콜라겐 비오틴 앰플 28일분 오간자 에디션+ 앰플 3입 추가 증정</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
           <t>[그레인온] 골드 카무트 브랜드밀 효소 3개월(+선물포장) +파로효소 그린캡슐레이션 증정</t>
         </is>
       </c>
-      <c r="D17" s="3" t="inlineStr">
-        <is>
-          <t>[리센느에디션] 베리말차 캡슐레이션 효소 1.8g 30포, 2개</t>
-        </is>
-      </c>
-      <c r="E17" s="3" t="inlineStr">
-        <is>
-          <t>'3입 증정' "선물하기 1등 콜라겐" 아일로 타입1 콜라겐 비오틴 앰플 28일분 오간자 에디션+ 앰플 3입 추가 증정</t>
-        </is>
-      </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
           <t>[그레인온] 골드 카무트 브랜드밀효소G 3개월분+10포증정(총100포) + 파로저당씬칩 증정</t>
@@ -4546,12 +4586,12 @@
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
+          <t>아르기닌 증정 남친 활력선물 대한민국 NO.1 김종국 트리플아르기닌 6200 (30포) + 아르기닌 추가 증정</t>
+        </is>
+      </c>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
           <t>아메리카노 증정 에너지 활력선물 [김종국 추천세트]익스트림 아르기닌정 (2개월분) &amp; 밀크씨슬 플러스 (2개월분) + 쇼핑백 증정</t>
-        </is>
-      </c>
-      <c r="L17" s="3" t="inlineStr">
-        <is>
-          <t>"이게 바로 찐! 초고함량" 액상스틱 L-아르기닌 7000 3박스 [케이스 동봉]</t>
         </is>
       </c>
     </row>
@@ -4599,13 +4639,13 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
+        <v>88</v>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>734</v>
+      </c>
+      <c r="E19" s="3" t="n">
         <v>1666</v>
-      </c>
-      <c r="D19" s="3" t="n">
-        <v>88</v>
-      </c>
-      <c r="E19" s="3" t="n">
-        <v>734</v>
       </c>
       <c r="F19" s="3" t="n">
         <v>873</v>
@@ -4623,10 +4663,10 @@
         <v>758</v>
       </c>
       <c r="K19" s="3" t="n">
+        <v>248</v>
+      </c>
+      <c r="L19" s="3" t="n">
         <v>1534</v>
-      </c>
-      <c r="L19" s="3" t="n">
-        <v>39</v>
       </c>
     </row>
     <row r="20" ht="90" customHeight="1">
@@ -4637,71 +4677,74 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>소화 개선 및 변비 완화 — 식후 소화 불량 해소에 도움을 주며 변비 증상이 좋아짐
-저렴한 가격과 덤 구성 — 가격이 착하고 파로효소 추가 증정 등 사은품 구성이 훌륭함
-고급스러운 선물 포장 — 선물용 포장이 깔끔하고 고급스러워 만족도가 높음</t>
+          <t>매력적인 굿즈 — 모델 리센느 원이의 포토카드와 사은품이 포함되어 팬들의 만족도가 높음
+맛있는 효소 섭취 — 평소 말차를 잘 못 먹는 사람도 거부감 없이 맛있게 먹을 수 있음</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>아이돌 굿즈와 풍성한 증정 — 리센느 원이 포토카드와 단백질 스낵 사은품이 동봉되어 구성이 혜자스러움
-맛있는 맛과 간편함 — 말차를 잘 못 먹는 사람도 맛있게 즐길 수 있는 맛이며 먹기 편함</t>
+          <t>정성 가득한 패키지 — 오간자 에디션의 고급스럽고 은은한 분홍빛 포장이 받는 사람을 기쁘게 함
+풍부한 추가 증정 — 무료 체험 앰플 및 추가 샘플이 들어 있어 구성이 더욱 풍부함
+피부 맑음 효과 — 꾸준히 마시면 피부가 한결 맑아지고 탱탱해지는 기분을 느낄 수 있음</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>예쁘고 고급스러운 포장 — 정성스럽고 은은한 고급 핑크 포장으로 선물 받는 사람의 기분을 좋게 함
-피부 개선 체감 효과 — 꾸준히 섭취 시 피부가 탱탱해지고 맑아지는 느낌을 받음
-섭취 편의성과 앰플 증정 — 마시기 편리한 용기 구조이며 추가 증정 앰플이 포함되어 만족스러움</t>
+          <t>원활한 배변 활동 — 폐경 이후 겪은 소화 불량과 만성 변비 증상이 섭취 후 많이 개선됨
+풍성한 추가 구성 — 파로효소 그린캡슐레이션 등 다양한 덤과 풍성한 사은품이 제공됨
+착한 세일 가격 — 정가 대비 톡딜 할인 혜택으로 저렴하고 합리적인 가격에 구매함</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>속 편한 소화 개선 효과 — 식후 복용 시 소화가 잘 되며 소화력이 떨어진 사람에게 효과적임
-우수한 가성비와 맛 — 맛이 좋고 저렴한 가격에 구매하여 쟁여두고 먹기 좋음
-풍성한 과자 사은품 증정 — 10포 추가 증정 외에도 파로저당씬칩 과자 선물이 제공됨</t>
+          <t>우수한 소화 개선 — 식후 복용 시 소화가 잘되며 나이 들어 저하된 소화력 보완에 효과적임
+높은 가성비 — 총 100포 구성에 파로저당씬칩까지 주면서 가격도 저렴해 실속 있음
+부담 없는 맛 — 효소 특유의 거부감 없이 고소하고 맛이 좋아 간식처럼 섭취함</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>다양한 구성과 골라먹는 재미 — 한 달 식단으로 다양한 맛이 들어있어 매일 골라 먹기 좋음
-착한 가격과 보냉백 증정 — 가격 대비 양이 넉넉하며 도시락용으로 유용한 보냉파우치가 함께 옴</t>
+          <t>훌륭한 가성비 — 30팩이라는 넉넉한 수량을 저렴한 균일 패키지 가격에 획득 가능함
+다양한 구성 — 여러 가지 맛이 섞여 있어 질리지 않고 매일 골라 먹는 재미가 있음
+유용한 보냉 가방 — 사은품으로 제공된 보냉백이 실용적이라 도시락용 가방으로 활용하기 좋음</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>부드러운 식감과 다양한 맛 — 뻑뻑함이 적고 양념이 맛있으며 구성이 다양해 질리지 않고 섭취함
-뛰어난 가성비와 조리 편의성 — 저렴한 가격에 넉넉한 갯수를 제공하며 전자레인지로 간편 조리가 가능함</t>
+          <t>부드러운 식감 — 닭가슴살 특유의 뻑뻑함이 덜하고 매우 촉촉하고 부드러움
+물리지 않는 맛 — 단조롭지 않고 자극적이지 않은 다양한 양념 구성으로 지속 섭취 가능함
+초특가 세트 — 24팩에 달하는 많은 양의 닭가슴살을 3만 원 이하로 저렴하게 구매함</t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>비린 맛 없는 부드러운 맛 — 단백질 특유의 비리거나 텁텁한 맛이 없고 일반 우유처럼 맛있음
-포만감과 편안한 속 — 운동 후 허기를 달래주며 마신 뒤에도 더부룩함 없이 속이 편함
-슬림한 용기의 높은 휴대성 — 패키지가 슬림하여 가방에 넣고 다니며 간편하게 챙겨 마시기 좋음</t>
+          <t>깔끔하고 맛있는 맛 — 단백질 음료 특유의 비리고 텁텁한 맛없이 진하고 달콤함
+포만감 및 영양 — 속을 더부룩하지 않게 하면서도 어느 정도 허기를 달래 주고 영양이 충분함
+슬림한 디자인 — 패키지가 슬림하여 가방에 휴대하여 언제 어디서든 꺼내 먹기 용이함</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>예쁜 케이스 디자인 — 케이스와 포장이 예뻐서 선물받을 때 만족감이 큼
-부담 없는 맛과 편의성 — 마시기 편리한 앰플 형태이며 비타민 음료 같은 맛으로 부담 없음</t>
+          <t>공주풍 예쁜 케이스 — 핑크빛 앰플 병과 외부 패키지가 공주 소품처럼 예뻐서 선물로 가치가 높음
+새콤하고 편한 섭취 — 비타 음료와 비슷한 새콤달콤한 맛이라 물 없이 앰플로 가볍게 복용함</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>확실한 피로 회복 효과 — 아침에 일어날 때 몸이 가벼워지고 일상 피로 완화에 도움 됨
-운동 집중도 및 활력 향상 — 운동 전에 챙겨 먹으면 쉽게 지치지 않고 운동 수행 능력에 도움이 됨
-알찬 세트 구성과 쇼핑백 — 아르기닌과 밀크씨슬 2개월분 구성에 쇼핑백이 포함되어 선물용으로 최고임</t>
+          <t>검증된 초고함량 — 1포당 L-아르기닌 6,200mg을 함유하여 운동 지구력과 기력 향상에 효과적임
+휴대성 좋은 포장 — 개별 스틱 포장으로 설계되어 언제든 챙겨 다니며 먹기 쉬움
+센스 있는 부속품 — 전용 쇼핑백과 여유분의 아르기닌 스틱이 추가 동봉되어 선물하기에 적절함</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>상큼한 레몬 맛과 간편 섭취 — 액상 타입이라 물에 타 먹기 편하고 레몬 맛이라 거부감이 없음
-우수한 휴대성과 활력 증진 — 스틱 제형으로 외출 시 챙기기 쉽고 아침 공복이나 운동 전 활력 충전에 좋음</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="60" customHeight="1">
+          <t>활력 있는 아침 — 섭취 후 아침 기상 시 몸이 한결 가볍고 일상생활의 피로가 줄어듦
+이상적인 성분 조화 — 간 건강을 돕는 밀크씨슬과 활력 충전을 주는 아르기닌을 함께 챙길 수 있음
+2개월의 넉넉한 양 — 2개월분 구성으로 오랜 기간 넉넉하게 본인의 건강을 관리하기 좋음</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="90" customHeight="1">
       <c r="B21" s="1" t="inlineStr">
         <is>
           <t>부정리뷰</t>
@@ -4709,36 +4752,38 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>구매 수량 제한의 아쉬움 — 1인당 구매 제한 갯수가 설정되어 있어 여러 명에게 선물하기에 수량이 모자람</t>
-        </is>
-      </c>
-      <c r="D21" s="3" t="inlineStr">
-        <is>
-          <t>포토카드 구성 불일치 — 안내와 달리 포토카드가 1장만 들어있거나 고정 수령이라 아쉬움
-배송 상태 불만족 — 제품 품질은 좋으나 배송 과정 및 처리가 불만족스러움</t>
-        </is>
-      </c>
-      <c r="E21" s="3" t="inlineStr"/>
+          <t>사은품 수량 오류 — 포토카드 두 장 제공 안내와 달리 실제로는 한 장만 동봉되어 배송됨
+불만족스러운 배송 — 배송 상태가 단정치 못하고 엉망으로 옴
+포토카드 고정형 — 포토카드가 랜덤 구성이 아닌 고정형 제품이라 아쉬움</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr"/>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>구매 수량 제한 — 한 번에 구매할 수 있는 수량이 한정되어 다수에게 선물하기 불편함</t>
+        </is>
+      </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>구매 갯수 제한의 아쉬움 — 지인 선물용으로 다량 구매 시 2개 수량 제한이 걸려 있어 아쉬움</t>
+          <t>구매 개수 제한 — 선물용으로 여러 개 사고 싶으나 수량 제한이 걸려 있어 불편함</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>포장 터짐 및 소스 누출 — 진공 포장이 헐렁하거나 제품이 터져 주변에 소스가 묻어옴
-배송 중 해동 발생 — 배송 시 냉동 상태가 제대로 유지되지 않고 녹아서 도착함</t>
+          <t>일부 포장 터짐 — 밀봉이 헐렁하게 포장되어 배송 중 제품 일부가 터져 소스가 흘러나옴
+제품 해동 배송 — 도착했을 때 냉동 상태가 풀려 닭가슴살이 많이 녹은 채로 수령함</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>배송 시 제품 해동 문제 — 배송 도착 상태에서 닭가슴살 제품이 전부 녹아서 도착함</t>
+          <t>배송 중 해동됨 — 완전 냉동 상태가 유지되지 않고 배송 과정에서 전부 녹아서 도착함</t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr"/>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>진한 농도와 즉각적 효과 미흡 — 마시기에 맛이 다소 진하여 물이 필요하고 단기 섭취 시 효과 체감이 적음</t>
+          <t>다소 강한 맛과 향 — 마실 때 맛이 다소 진하고 목 넘김 후 강해 물을 곁들여 마셔야 함
+미미한 초기 효과 — 단기간 섭취 기준으로는 눈에 띄는 즉각적인 변화가 잘 보이지 않음</t>
         </is>
       </c>
       <c r="K21" s="3" t="inlineStr"/>
@@ -4752,19 +4797,19 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
+          <t>24,900원</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>65,900원</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
           <t>43,900원</t>
         </is>
       </c>
-      <c r="D22" s="3" t="inlineStr">
-        <is>
-          <t>24,900원</t>
-        </is>
-      </c>
-      <c r="E22" s="3" t="inlineStr">
-        <is>
-          <t>65,900원</t>
-        </is>
-      </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
           <t>19,900원</t>
@@ -4792,12 +4837,12 @@
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
+          <t>43,900원</t>
+        </is>
+      </c>
+      <c r="L22" s="3" t="inlineStr">
+        <is>
           <t>25,900원</t>
-        </is>
-      </c>
-      <c r="L22" s="3" t="inlineStr">
-        <is>
-          <t>30,900원</t>
         </is>
       </c>
     </row>
@@ -4995,49 +5040,49 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>[신혜선 PICK] 동국 마이팝 푸룬＆식이섬유</t>
+          <t>홀베리 유기농 엑스트라버진 올리브유 10포</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>홀베리</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2,000원</t>
+          <t>5,000원</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=610911029&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=032640075&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260623/QaObI3LjZ86tREQcCYCw610911029_00_00QaObI3LjZ86tREQcCYCw.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260312/0RECqyOK2V8qTztn2K7E032640075_00_000RECqyOK2V8qTztn2K7E.jpg</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="J2" t="n">
-        <v>446</v>
+        <v>1016</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>가성비와 편리한 섭취 — 가격이 저렴하고 많이 달지 않아 푸룬 주스 중 가장 편하게 먹을 수 있음</t>
+          <t>개별 소포장 편의성 — 스틱 포로 설계되어 휴대성이 뛰어나며 야외에서도 위생적으로 먹을 수 있음</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>복통 없는 장 비움 효과 — 배 아픔 없이 깔끔하게 속을 비워주는 데 도움을 줌</t>
+          <t>식단 및 요리 활용 — 아침 다이어트 식단에 곁들이거나 부엌에서 풍미를 더하는 요리용 기름으로 유용함</t>
         </is>
       </c>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
-          <t>호불호 갈리는 냄새와 효과 — 냄새에 민감한 경우 거부감이 들 수 있으며 장 비움 효과가 미미할 수 있음</t>
+          <t>맵고 강한 맛 — 올리브유 특유의 매운맛과 향이 다소 강해 단독 섭취 시 자극적임</t>
         </is>
       </c>
       <c r="O2" t="inlineStr"/>
@@ -5046,7 +5091,7 @@
     <row r="3" ht="38" customHeight="1">
       <c r="B3" t="inlineStr">
         <is>
-          <t>혈행</t>
+          <t>비타민D</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -5054,12 +5099,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>대웅제약 코엔자임 Q10 30캡슐 30일분</t>
+          <t>오브맘 비타민D＆아연 하루구미 30일분</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>대웅제약</t>
+          <t>오브맘</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -5069,43 +5114,43 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000144&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=613602130&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250408/OqDM0kpIHoqFD3okk28W600000144_00_00OqDM0kpIHoqFD3okk28W.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250922/dxtu28UFPhWKbi5IG3n8613602130_00_01dxtu28UFPhWKbi5IG3n8.jpg</t>
         </is>
       </c>
       <c r="I3" t="n">
         <v>4.8</v>
       </c>
       <c r="J3" t="n">
-        <v>6450</v>
+        <v>1510</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>최고의 가성비와 접근성 — 다이소에서 저렴하게 구매하여 부담 없이 매일 꾸준히 먹기 좋음</t>
+          <t>맛있는 간식 대용 — 영양제 느낌 없이 맛있게 씹어 삼킬 수 있어 매일 편리하게 먹을 수 있음</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>일상 건강 및 혈압 관리 — 가슴 떨림이나 혈압 관리를 위해 꾸준히 재구매하며 건강을 챙김</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>대용량 제품의 부재 — 30일분 단위로만 판매되어 더 큰 대용량 구성이 없는 점이 아쉬움</t>
-        </is>
-      </c>
+          <t>아연과 비타민 복합 — 성장에 필수적인 비타민D와 아연을 한번에 섭취할 수 있어 유용함</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>뛰어난 가성비 — 다이소 특유의 합리적이고 저렴한 가격에 건강을 챙길 수 있음</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
     </row>
     <row r="4" ht="38" customHeight="1">
       <c r="B4" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>루테인/눈건강</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -5113,58 +5158,54 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>[의약외품] 동화 퀵앤써액 복숭아 12ml 5포</t>
+          <t>안국약품 토비콤 루테인 지아잔틴 미니 30캡슐</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>동화약품</t>
+          <t>안국약품</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>3,000원</t>
+          <t>5,000원</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=601618634&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=611982831&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260424/G3OpB4vFrKk7H6gBBjO3601618634_00_00G3OpB4vFrKk7H6gBBjO3.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250623/lX1R9GhsEUzz72XUg7VZ611982831_00_00lX1R9GhsEUzz72XUg7VZ.jpg</t>
         </is>
       </c>
       <c r="I4" t="n">
         <v>4.8</v>
       </c>
       <c r="J4" t="n">
-        <v>770</v>
+        <v>1420</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>빠른 피로 회복과 좋은 맛 — 복숭아 맛으로 맛있으며 출근길이나 피곤할 때 가볍게 먹어 피로를 풀기 좋음</t>
+          <t>작은 미니 캡슐 — 알약의 크기가 미니 사이즈라 목 구멍이 좁은 사람도 쉽게 삼킴</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>부담 없는 개당 가격 — 개당 600원 꼴의 저렴한 가격으로 부담 없이 시도하기 좋음</t>
+          <t>최상의 가격 혜택 — 다이소 가격 책정으로 타사 대비 저렴하게 눈 건강 영양제를 구입함</t>
         </is>
       </c>
       <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>혀 착색과 약 특유의 쓴맛 — 섭취 후 혀가 노랗게 착색되거나 약 특유의 쓴맛이 느껴질 수 있음</t>
-        </is>
-      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
     </row>
     <row r="5" ht="38" customHeight="1">
       <c r="B5" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>홍삼/인삼</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -5172,58 +5213,58 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>자연관 정성담은 배도라지스틱 12포</t>
+          <t>휴럼 하루한포 6년근 고려홍삼 5포 5일분</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>자연관</t>
+          <t>휴럼</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>2,000원</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=901762093&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=919157053&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260508/SdledEzpIdjdFFQW6W8g901762093_00_00SdledEzpIdjdFFQW6W8g.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260327/PrU3TzDbYVJKWXoKyRxC919157053_00_01PrU3TzDbYVJKWXoKyRxC.jpg</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="J5" t="n">
-        <v>860</v>
+        <v>657</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>환절기 기관지 케어 — 목이 아프거나 환절기 기관지 건강을 챙길 때 효과가 있음</t>
+          <t>검증된 체력 개선 — 섭취한 날과 먹지 않은 날의 컨디션 및 피로도 차이를 실제로 느낌</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>저렴한 가격과 섭취 편의성 — 가격이 저렴하고 스틱 형태라 휴대하며 챙겨 먹기 편함</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>맛에 대한 호불호 존재 — 개인에 따라 맛에 대한 호불호가 갈릴 수 있음</t>
-        </is>
-      </c>
+          <t>훌륭한 가격 혜택 — 6년근 홍삼을 부담스럽지 않은 아주 착하고 저렴한 가격에 먹을 수 있음</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>스틱형 편리성 — 흘림 없는 액체형 파우치 포장이라 복용 과정이 매끄럽고 간편함</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
     </row>
     <row r="6" ht="38" customHeight="1">
       <c r="B6" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>혈행</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -5231,12 +5272,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>락피도 티니핑 빌베리스틱 12포 12일분</t>
+          <t>대웅제약 코엔자임 Q10 30캡슐 30일분</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>락피도</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -5246,34 +5287,30 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=951817123&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000144&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260226/7axcAyeOWQh7bg9XboNV951817123_00_017axcAyeOWQh7bg9XboNV.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/OqDM0kpIHoqFD3okk28W600000144_00_00OqDM0kpIHoqFD3okk28W.png</t>
         </is>
       </c>
       <c r="I6" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="J6" t="n">
-        <v>297</v>
+        <v>6458</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>맛있는 블루베리 맛 — 아이와 어른 모두 좋아하는 맛있는 블루베리 맛으로 젤리 대신 섭취함</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>편리한 스틱 포장 — 하나씩 편하게 꺼내 먹을 수 있는 낱개 포장이라 간편함</t>
-        </is>
-      </c>
+          <t>독보적인 가성비 — 코엔자임 Q10 제품을 저렴한 가성비로 오랫동안 지속해서 사 먹기 좋음</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
-          <t>아이 기호에 따른 섭취 차이 — 생각보다 아이가 잘 먹지 않는 경우가 있음</t>
+          <t>체질 미스 매칭 — 개인의 몸 상태나 체질에 따라 제품이 맞지 않는 상황이 발생할 수 있음</t>
         </is>
       </c>
       <c r="O6" t="inlineStr"/>
@@ -5282,7 +5319,7 @@
     <row r="7" ht="38" customHeight="1">
       <c r="B7" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>비타민D</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -5290,58 +5327,58 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>닥터블릿 푸응 7days 데일리버닝 14포 7일분</t>
+          <t>대웅제약 비타민D 4000IU 30정 30일분</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>닥터블릿</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>3,000원</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=286314174&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000132&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260625/KRdkveXe1tokHnITW5go286314174_00_00KRdkveXe1tokHnITW5go.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/SvY5chCvz0QZIyP7AdTc600000132_00_00SvY5chCvz0QZIyP7AdTc.png</t>
         </is>
       </c>
       <c r="I7" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="J7" t="n">
-        <v>489</v>
+        <v>2900</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>원활한 배변 활동 도움 — 식후에 챙겨 먹기 좋으며 화장실을 잘 가도록 도와줌</t>
+          <t>고함량 스펙 — 결핍되기 쉬운 영양 보충을 위해 4000IU 고함량으로 확실하게 설계됨</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>부담 없는 저렴한 가격 — 다이소 특유의 저렴한 가격으로 부담 없이 구매함</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>낮은 용해도와 약 맛 — 물에 잘 녹지 않고 레몬향 속에 사카린 맛이나 약 맛이 느껴짐</t>
-        </is>
-      </c>
+          <t>전문가 추천 제품 — 약사와 유튜브 크리에이터들이 가성비 영양제로 추천하여 신뢰성이 높음</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>저렴한 비용 섭취 — 다이소 유통망을 통해 거품 없는 가격에 건강을 챙길 수 있어 짱임</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr"/>
     </row>
     <row r="8" ht="38" customHeight="1">
       <c r="B8" t="inlineStr">
         <is>
-          <t>비타민C/항산화</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -5349,43 +5386,43 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>동국제약 리포좀 비타민C 30정</t>
+          <t>대웅제약 바나바잎 추출물 30정 30일분</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>3,000원</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=610910679&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000131&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250829/3zNHA2Xp859SKsazXUwt610910679_00_003zNHA2Xp859SKsazXUwt.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/rCiQaBH4VQ1rKKr7rz83600000131_00_00rCiQaBH4VQ1rKKr7rz83.png</t>
         </is>
       </c>
       <c r="I8" t="n">
         <v>4.8</v>
       </c>
       <c r="J8" t="n">
-        <v>1081</v>
+        <v>4654</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>리포좀 비타민의 높은 가성비 — 흡수율이 뛰어난 리포좀 비타민C를 저렴한 가격에 겟할 수 있음</t>
+          <t>유튜브 추천 제품 — 검증된 건강 채널 및 유튜브 후기 추천을 통해 구매 신뢰도가 상승함</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>믿고 구매하는 브랜드 — 동국제약 제품이라 신뢰하고 떨어질 때마다 매번 구매하여 복용함</t>
+          <t>부담 없는 재구매 — 비용 부담이 적어 벌써 세 번째 재구매를 할 만큼 장기 섭취에 편안함</t>
         </is>
       </c>
       <c r="M8" t="inlineStr"/>
@@ -5396,7 +5433,7 @@
     <row r="9" ht="38" customHeight="1">
       <c r="B9" t="inlineStr">
         <is>
-          <t>비타민D</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -5404,52 +5441,56 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>대웅제약 비타민D 4000IU 30정 30일분</t>
+          <t>안국약품 콜린 미오이노시톨 4000 10포</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>대웅제약</t>
+          <t>안국약품</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>3,000원</t>
+          <t>5,000원</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000132&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=985472642&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250408/SvY5chCvz0QZIyP7AdTc600000132_00_00SvY5chCvz0QZIyP7AdTc.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250623/yivvMAKVS3Hyi026FPyX985472642_00_00yivvMAKVS3Hyi026FPyX.jpg</t>
         </is>
       </c>
       <c r="I9" t="n">
         <v>4.8</v>
       </c>
       <c r="J9" t="n">
-        <v>2899</v>
+        <v>1978</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>고함량 대비 훌륭한 가성비 — 4000IU 고함량 비타민D를 매우 저렴하게 구매할 수 있어 만족스러움</t>
+          <t>합리적인 이노시톨 — 시중의 고가 이노시톨 대신 5,000원의 저렴한 예산으로 간편하게 시작 가능함</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>쉬운 섭취와 높은 신뢰도 — 알약 먹기가 편하며 약사 추천 등으로 신뢰도가 높아 자주 재구매함</t>
+          <t>레모나 맛의 청량함 — 레몬 맛 가루로 설계되어 신맛을 즐기며 맛있게 먹기 유용함</t>
         </is>
       </c>
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
-          <t>널널한 상자 내부 포장 — 제품 겉 박스 크기에 비해 내부 상자 공간이 다소 널널하게 남아 있음</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr"/>
+          <t>아쉬운 포장 분량 — 흡수율을 위해 하루 두 번으로 세분하여 2000mg씩 나눠서 소포장했으면 좋겠음</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>빠른 한 통 소진 — 10포 구성이라서 복용한 지 열흘 만에 다 마셔버려 너무 빨리 줄어듦</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr"/>
     </row>
     <row r="10" ht="38" customHeight="1">
@@ -5463,12 +5504,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>대웅제약 철분 30정 30일분</t>
+          <t>동국 맛있는 샐러드 미니볼 15포 15일분</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>대웅제약</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -5478,43 +5519,47 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000133&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=610910891&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260820/ahWGJ6KpupAlwxw7p3xm600000133_00_00ahWGJ6KpupAlwxw7p3xm.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260312/tgDz0oHoOLB3gj3BLgFd610910891_00_01tgDz0oHoOLB3gj3BLgFd.png</t>
         </is>
       </c>
       <c r="I10" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="J10" t="n">
-        <v>2349</v>
+        <v>2167</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>다이소 접근성과 뛰어난 가성비 — 다이소 매장에서 간편히 살 수 있으며 타사 대비 가성비가 훌륭함</t>
+          <t>야채 영양의 단순화 — 손이 잘 가지 않는 과채류를 하루 1포로 간편하고 가볍게 대체 섭취함</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>화사한 핑크색 정제 — 알약 색상이 핑크색이라 예쁘며 무난하게 챙겨 먹기 좋음</t>
+          <t>건강한 입가심 — 입이 허전할 때 일반 불량 과자 대신 상큼달달한 대체물로 활용함</t>
         </is>
       </c>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
-          <t>복합 성분 구성의 아쉬움 — 다른 성분 없이 철분만 단독으로 들어있었으면 하는 아쉬움이 있음</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr"/>
+          <t>불안정한 맛 선호 — 달콤한 캔디류라 생각하면 다소 맛이 덜하며 야채 알약의 타협된 맛임</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>딱딱한 볼 제형 — 생각했던 것보다 알갱이의 질감이 약간 굳어 있어 씹을 때 딱딱함</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr"/>
     </row>
     <row r="11" ht="38" customHeight="1">
       <c r="B11" t="inlineStr">
         <is>
-          <t>비타민C/항산화</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -5522,51 +5567,47 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>대웅제약 비타민C 30정 30일분</t>
+          <t>종근당 데일리와이즈 혈당컷 다이어트 12정 12일분</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>대웅제약</t>
+          <t>종근당</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>2,000원</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000127&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=032306201&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250408/V0qSVbLLgSaCWbYWEu73600000127_00_00V0qSVbLLgSaCWbYWEu73.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260406/NBw0phjtTvR7tEfBicGr032306201_00_01NBw0phjtTvR7tEfBicGr.jpg</t>
         </is>
       </c>
       <c r="I11" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="J11" t="n">
-        <v>2641</v>
+        <v>1213</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>영국산 비타민C의 독보적 가성비 — 영국산 고함량 비타민C를 이 가격에 구매할 수 있어 가성비가 최고임</t>
+          <t>배변 활동의 수월성 — 복용 후 속이 편안해지고 화장실을 원활하게 가는 개선 효과를 경험함</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>체감되는 섭취 효과 — 안 먹을 때와 차이가 확연히 느껴져 꼭 챙겨 먹게 됨</t>
+          <t>견고한 포장 재질 — 파우치와 박스의 이음새 및 마감이 매우 튼튼하게 이루어져 안심됨</t>
         </is>
       </c>
       <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>배송 시 겉포장 구겨짐 — 배송 과정에서 겉 박스 포장이 다소 찌그러져 도착함</t>
-        </is>
-      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
     </row>
@@ -5686,47 +5727,47 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
+          <t>비타민D</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>루테인/눈건강</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>홍삼/인삼</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
           <t>혈행</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>비타민D</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>다이어트/체중관리</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
         <is>
           <t>기타/특수목적</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="K3" s="3" t="inlineStr">
         <is>
           <t>기타/특수목적</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>비타민C/항산화</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>비타민D</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>비타민C/항산화</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
     </row>
@@ -5738,52 +5779,52 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
+          <t>홀베리</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>오브맘</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>안국약품</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>휴럼</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>대웅제약</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>대웅제약</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>대웅제약</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>안국약품</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
           <t>동국제약</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>대웅제약</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>동화약품</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>자연관</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>락피도</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>닥터블릿</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>동국제약</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>대웅제약</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>대웅제약</t>
-        </is>
-      </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>대웅제약</t>
+          <t>종근당</t>
         </is>
       </c>
     </row>
@@ -5795,52 +5836,52 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>[신혜선 PICK] 동국 마이팝 푸룬＆식이섬유</t>
+          <t>홀베리 유기농 엑스트라버진 올리브유 10포</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
+          <t>오브맘 비타민D＆아연 하루구미 30일분</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>안국약품 토비콤 루테인 지아잔틴 미니 30캡슐</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>휴럼 하루한포 6년근 고려홍삼 5포 5일분</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
           <t>대웅제약 코엔자임 Q10 30캡슐 30일분</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>[의약외품] 동화 퀵앤써액 복숭아 12ml 5포</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>자연관 정성담은 배도라지스틱 12포</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>락피도 티니핑 빌베리스틱 12포 12일분</t>
-        </is>
-      </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>닥터블릿 푸응 7days 데일리버닝 14포 7일분</t>
+          <t>대웅제약 비타민D 4000IU 30정 30일분</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>동국제약 리포좀 비타민C 30정</t>
+          <t>대웅제약 바나바잎 추출물 30정 30일분</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>대웅제약 비타민D 4000IU 30정 30일분</t>
+          <t>안국약품 콜린 미오이노시톨 4000 10포</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>대웅제약 철분 30정 30일분</t>
+          <t>동국 맛있는 샐러드 미니볼 15포 15일분</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>대웅제약 비타민C 30정 30일분</t>
+          <t>종근당 데일리와이즈 혈당컷 다이어트 12정 12일분</t>
         </is>
       </c>
     </row>
@@ -5851,7 +5892,7 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="D6" s="3" t="n">
         <v>4.8</v>
@@ -5860,13 +5901,13 @@
         <v>4.8</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="I6" s="3" t="n">
         <v>4.8</v>
@@ -5875,10 +5916,10 @@
         <v>4.8</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="7">
@@ -5888,37 +5929,37 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>446</v>
+        <v>1016</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>6450</v>
+        <v>1510</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>770</v>
+        <v>1420</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>860</v>
+        <v>657</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>297</v>
+        <v>6458</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>489</v>
+        <v>2900</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>1081</v>
+        <v>4654</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>2899</v>
+        <v>1978</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>2349</v>
+        <v>2167</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>2641</v>
-      </c>
-    </row>
-    <row r="8" ht="60" customHeight="1">
+        <v>1213</v>
+      </c>
+    </row>
+    <row r="8" ht="90" customHeight="1">
       <c r="B8" s="1" t="inlineStr">
         <is>
           <t>긍정리뷰</t>
@@ -5926,66 +5967,68 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>가성비와 편리한 섭취 — 가격이 저렴하고 많이 달지 않아 푸룬 주스 중 가장 편하게 먹을 수 있음
-복통 없는 장 비움 효과 — 배 아픔 없이 깔끔하게 속을 비워주는 데 도움을 줌</t>
+          <t>개별 소포장 편의성 — 스틱 포로 설계되어 휴대성이 뛰어나며 야외에서도 위생적으로 먹을 수 있음
+식단 및 요리 활용 — 아침 다이어트 식단에 곁들이거나 부엌에서 풍미를 더하는 요리용 기름으로 유용함</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>최고의 가성비와 접근성 — 다이소에서 저렴하게 구매하여 부담 없이 매일 꾸준히 먹기 좋음
-일상 건강 및 혈압 관리 — 가슴 떨림이나 혈압 관리를 위해 꾸준히 재구매하며 건강을 챙김</t>
+          <t>맛있는 간식 대용 — 영양제 느낌 없이 맛있게 씹어 삼킬 수 있어 매일 편리하게 먹을 수 있음
+아연과 비타민 복합 — 성장에 필수적인 비타민D와 아연을 한번에 섭취할 수 있어 유용함
+뛰어난 가성비 — 다이소 특유의 합리적이고 저렴한 가격에 건강을 챙길 수 있음</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>빠른 피로 회복과 좋은 맛 — 복숭아 맛으로 맛있으며 출근길이나 피곤할 때 가볍게 먹어 피로를 풀기 좋음
-부담 없는 개당 가격 — 개당 600원 꼴의 저렴한 가격으로 부담 없이 시도하기 좋음</t>
+          <t>작은 미니 캡슐 — 알약의 크기가 미니 사이즈라 목 구멍이 좁은 사람도 쉽게 삼킴
+최상의 가격 혜택 — 다이소 가격 책정으로 타사 대비 저렴하게 눈 건강 영양제를 구입함</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>환절기 기관지 케어 — 목이 아프거나 환절기 기관지 건강을 챙길 때 효과가 있음
-저렴한 가격과 섭취 편의성 — 가격이 저렴하고 스틱 형태라 휴대하며 챙겨 먹기 편함</t>
+          <t>검증된 체력 개선 — 섭취한 날과 먹지 않은 날의 컨디션 및 피로도 차이를 실제로 느낌
+훌륭한 가격 혜택 — 6년근 홍삼을 부담스럽지 않은 아주 착하고 저렴한 가격에 먹을 수 있음
+스틱형 편리성 — 흘림 없는 액체형 파우치 포장이라 복용 과정이 매끄럽고 간편함</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>맛있는 블루베리 맛 — 아이와 어른 모두 좋아하는 맛있는 블루베리 맛으로 젤리 대신 섭취함
-편리한 스틱 포장 — 하나씩 편하게 꺼내 먹을 수 있는 낱개 포장이라 간편함</t>
+          <t>독보적인 가성비 — 코엔자임 Q10 제품을 저렴한 가성비로 오랫동안 지속해서 사 먹기 좋음</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>원활한 배변 활동 도움 — 식후에 챙겨 먹기 좋으며 화장실을 잘 가도록 도와줌
-부담 없는 저렴한 가격 — 다이소 특유의 저렴한 가격으로 부담 없이 구매함</t>
+          <t>고함량 스펙 — 결핍되기 쉬운 영양 보충을 위해 4000IU 고함량으로 확실하게 설계됨
+전문가 추천 제품 — 약사와 유튜브 크리에이터들이 가성비 영양제로 추천하여 신뢰성이 높음
+저렴한 비용 섭취 — 다이소 유통망을 통해 거품 없는 가격에 건강을 챙길 수 있어 짱임</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>리포좀 비타민의 높은 가성비 — 흡수율이 뛰어난 리포좀 비타민C를 저렴한 가격에 겟할 수 있음
-믿고 구매하는 브랜드 — 동국제약 제품이라 신뢰하고 떨어질 때마다 매번 구매하여 복용함</t>
+          <t>유튜브 추천 제품 — 검증된 건강 채널 및 유튜브 후기 추천을 통해 구매 신뢰도가 상승함
+부담 없는 재구매 — 비용 부담이 적어 벌써 세 번째 재구매를 할 만큼 장기 섭취에 편안함</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>고함량 대비 훌륭한 가성비 — 4000IU 고함량 비타민D를 매우 저렴하게 구매할 수 있어 만족스러움
-쉬운 섭취와 높은 신뢰도 — 알약 먹기가 편하며 약사 추천 등으로 신뢰도가 높아 자주 재구매함</t>
+          <t>합리적인 이노시톨 — 시중의 고가 이노시톨 대신 5,000원의 저렴한 예산으로 간편하게 시작 가능함
+레모나 맛의 청량함 — 레몬 맛 가루로 설계되어 신맛을 즐기며 맛있게 먹기 유용함</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>다이소 접근성과 뛰어난 가성비 — 다이소 매장에서 간편히 살 수 있으며 타사 대비 가성비가 훌륭함
-화사한 핑크색 정제 — 알약 색상이 핑크색이라 예쁘며 무난하게 챙겨 먹기 좋음</t>
+          <t>야채 영양의 단순화 — 손이 잘 가지 않는 과채류를 하루 1포로 간편하고 가볍게 대체 섭취함
+건강한 입가심 — 입이 허전할 때 일반 불량 과자 대신 상큼달달한 대체물로 활용함</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>영국산 비타민C의 독보적 가성비 — 영국산 고함량 비타민C를 이 가격에 구매할 수 있어 가성비가 최고임
-체감되는 섭취 효과 — 안 먹을 때와 차이가 확연히 느껴져 꼭 챙겨 먹게 됨</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
+          <t>배변 활동의 수월성 — 복용 후 속이 편안해지고 화장실을 원활하게 가는 개선 효과를 경험함
+견고한 포장 재질 — 파우치와 박스의 이음새 및 마감이 매우 튼튼하게 이루어져 안심됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="60" customHeight="1">
       <c r="B9" s="1" t="inlineStr">
         <is>
           <t>부정리뷰</t>
@@ -5993,50 +6036,32 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>호불호 갈리는 냄새와 효과 — 냄새에 민감한 경우 거부감이 들 수 있으며 장 비움 효과가 미미할 수 있음</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>대용량 제품의 부재 — 30일분 단위로만 판매되어 더 큰 대용량 구성이 없는 점이 아쉬움</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>혀 착색과 약 특유의 쓴맛 — 섭취 후 혀가 노랗게 착색되거나 약 특유의 쓴맛이 느껴질 수 있음</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>맛에 대한 호불호 존재 — 개인에 따라 맛에 대한 호불호가 갈릴 수 있음</t>
-        </is>
-      </c>
+          <t>맵고 강한 맛 — 올리브유 특유의 매운맛과 향이 다소 강해 단독 섭취 시 자극적임</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr"/>
+      <c r="E9" s="3" t="inlineStr"/>
+      <c r="F9" s="3" t="inlineStr"/>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>아이 기호에 따른 섭취 차이 — 생각보다 아이가 잘 먹지 않는 경우가 있음</t>
-        </is>
-      </c>
-      <c r="H9" s="3" t="inlineStr">
-        <is>
-          <t>낮은 용해도와 약 맛 — 물에 잘 녹지 않고 레몬향 속에 사카린 맛이나 약 맛이 느껴짐</t>
-        </is>
-      </c>
+          <t>체질 미스 매칭 — 개인의 몸 상태나 체질에 따라 제품이 맞지 않는 상황이 발생할 수 있음</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="inlineStr"/>
       <c r="I9" s="3" t="inlineStr"/>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>널널한 상자 내부 포장 — 제품 겉 박스 크기에 비해 내부 상자 공간이 다소 널널하게 남아 있음</t>
+          <t>아쉬운 포장 분량 — 흡수율을 위해 하루 두 번으로 세분하여 2000mg씩 나눠서 소포장했으면 좋겠음
+빠른 한 통 소진 — 10포 구성이라서 복용한 지 열흘 만에 다 마셔버려 너무 빨리 줄어듦</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>복합 성분 구성의 아쉬움 — 다른 성분 없이 철분만 단독으로 들어있었으면 하는 아쉬움이 있음</t>
-        </is>
-      </c>
-      <c r="L9" s="3" t="inlineStr">
-        <is>
-          <t>배송 시 겉포장 구겨짐 — 배송 과정에서 겉 박스 포장이 다소 찌그러져 도착함</t>
-        </is>
-      </c>
+          <t>불안정한 맛 선호 — 달콤한 캔디류라 생각하면 다소 맛이 덜하며 야채 알약의 타협된 맛임
+딱딱한 볼 제형 — 생각했던 것보다 알갱이의 질감이 약간 굳어 있어 씹을 때 딱딱함</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="B10" s="1" t="inlineStr">
@@ -6046,52 +6071,52 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
+          <t>5,000원</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>5,000원</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>5,000원</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
           <t>2,000원</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="G10" s="3" t="inlineStr">
         <is>
           <t>5,000원</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
+      <c r="H10" s="3" t="inlineStr">
         <is>
           <t>3,000원</t>
         </is>
       </c>
-      <c r="F10" s="3" t="inlineStr">
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>3,000원</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
         <is>
           <t>5,000원</t>
         </is>
       </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t>5,000원</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>5,000원</t>
-        </is>
-      </c>
-      <c r="I10" s="3" t="inlineStr">
-        <is>
-          <t>5,000원</t>
-        </is>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
+      <c r="K10" s="3" t="inlineStr">
         <is>
           <t>3,000원</t>
         </is>
       </c>
-      <c r="K10" s="3" t="inlineStr">
-        <is>
-          <t>3,000원</t>
-        </is>
-      </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>2,000원</t>
         </is>
       </c>
     </row>
@@ -6278,7 +6303,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>[9월 올영픽] 고려은단 비타민C1000 이지+비타민D 120정 (+마이멜로디 파우치) (60일분)</t>
+          <t>고려은단 비타민C1000 600정 (20개월분)</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -6288,35 +6313,23 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>10,900원</t>
+          <t>42,900원</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000164736&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=1</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000225938&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=1</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0016/A00000016473622ko.png?l=ko</t>
-        </is>
-      </c>
-      <c r="I2" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="J2" t="n">
-        <v>15548</v>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>비타민C와 D의 효율적 조합 — 비타민B 트러블 걱정 없이 면역력과 실내 비타민D 부족을 동시에 챙김</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>높은 브랜드 신뢰도와 가성비 — 대한민국 1등 비타민 브랜드로서 높은 가성비와 확실한 효과를 제공함</t>
-        </is>
-      </c>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0022/A00000022593803ko.jpg?l=ko</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
@@ -6325,7 +6338,7 @@
     <row r="3" ht="38" customHeight="1">
       <c r="B3" t="inlineStr">
         <is>
-          <t>프로바이오틱스/유산균</t>
+          <t>비타민C/항산화</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -6333,34 +6346,34 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>덴프스 덴마크 유산균이야기 우먼 2개월분(질유산균) + 철분 헤모케어 3포 증정</t>
+          <t>[9월 올영픽] 고려은단 비타민C1000 이지+비타민D 120정 (+마이멜로디 파우치) (60일분)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>덴프스</t>
+          <t>고려은단</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>31,400원</t>
+          <t>10,900원</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000202658&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=2</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000164736&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=2</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020265829ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0016/A00000016473622ko.png?l=ko</t>
         </is>
       </c>
       <c r="I3" t="n">
         <v>4.9</v>
       </c>
       <c r="J3" t="n">
-        <v>8168</v>
+        <v>15549</v>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
@@ -6400,14 +6413,30 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024587418ko.jpg?l=ko</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024587419ko.jpg?l=ko</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J4" t="n">
+        <v>4819</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>유연한 섭취 루틴 — 아침 공복의 캡슐 오일부터 간식 형태의 콜라겐 구미까지 라이프에 맞게 다양함</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>가성비 정기 세일 — 올영 세일 기간에 할인쿠폰을 중복하여 사용하면 한층 경제적으로 쟁여둠</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>수분 피로 동시 케어 — 구덕하고 무거운 제형 대신 탄산수나 물에 섞는 형태로 청량하게 보충함</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
@@ -6415,7 +6444,7 @@
     <row r="5" ht="38" customHeight="1">
       <c r="B5" t="inlineStr">
         <is>
-          <t>비타민C/항산화</t>
+          <t>프로바이오틱스/유산균</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -6423,37 +6452,41 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>[9월 올영픽] 고려은단 메가도스C 비타민C 3000mg 30포 (+헬로키티 파우치)</t>
+          <t>덴프스 덴마크 유산균이야기 우먼 2개월분(질유산균) + 철분 헤모케어 3포 증정</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>고려은단</t>
+          <t>덴프스</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>9,900원</t>
+          <t>31,400원</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000187268&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=4</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000202658&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=4</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0018/A00000018726811ko.png?l=ko</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="J5" t="n">
-        <v>5753</v>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020265829ko.jpg?l=ko</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>공복 건강 스타트 — 아침 기상 후 공복 상태에서 물 한 컵과 함께 편하게 습관화하기 좋음</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>소장 욕구 굿즈 — 세계 1등 유산균의 메리트에 더해 공유 포토카드와 캐릭터 키링 등을 함께 줌</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
@@ -6493,19 +6526,35 @@
           <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020014347ko.jpg?l=ko</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
+      <c r="I6" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J6" t="n">
+        <v>12559</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>가스 없는 편안함 — 100억 유산균 보장으로 배 아픔이나 복부 가스 참 현상 없이 장이 편안함</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>귀여운 산리오 콜라보 — 인기 캐릭터 산리오 디자인 패키지와 전용 러기지택 증정 혜택으로 흥미를 유발함</t>
+        </is>
+      </c>
       <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>다소 큼직한 제형 — 기존에 평범하게 복용하던 타 영양제에 비해 알약의 물리적 두께가 있는 편임</t>
+        </is>
+      </c>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
     </row>
     <row r="7" ht="38" customHeight="1">
       <c r="B7" t="inlineStr">
         <is>
-          <t>프로바이오틱스/유산균</t>
+          <t>비타민C/항산화</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -6513,45 +6562,33 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>[덴프스] 덴마크 유산균이야기 30캡슐 1+1 기획 (+트루바이타민 3포 증정)</t>
+          <t>[9월 올영픽] 고려은단 메가도스C 비타민C 3000mg 30포 (+헬로키티 파우치)</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>덴프스</t>
+          <t>고려은단</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>30,400원</t>
+          <t>9,900원</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000206861&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=6</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000187268&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=6</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020686148ko.jpg?l=ko</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="J7" t="n">
-        <v>24395</v>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>장 건강 및 면역력 관리 — 아침 공복에 물과 섭취 시 장 건강 및 면역력 케어에 우수한 효과를 보임</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>1일 1캡슐과 알찬 기획 — 하루 한 알로 간편하게 섭취하며 1+1 기획으로 두 달간 경제적으로 복용 가능함</t>
-        </is>
-      </c>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0018/A00000018726811ko.png?l=ko</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
@@ -6560,7 +6597,7 @@
     <row r="8" ht="38" customHeight="1">
       <c r="B8" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>프로바이오틱스/유산균</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -6568,27 +6605,27 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>[딥트3일/남규리Pick]남규리의 바른 효소 리셋 8포</t>
+          <t>[덴프스] 덴마크 유산균이야기 30캡슐 1+1 기획 (+트루바이타민 3포 증정)</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>딥트3일</t>
+          <t>덴프스</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>16,000원</t>
+          <t>30,400원</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000211396&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=7</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000206861&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=7</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0021/A00000021139617ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020686148ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -6603,7 +6640,7 @@
     <row r="9" ht="38" customHeight="1">
       <c r="B9" t="inlineStr">
         <is>
-          <t>비타민C/항산화</t>
+          <t>프로바이오틱스/유산균</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -6611,34 +6648,50 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>[산리오 에디션] 올더베러 비타민C 구미 60구미 (30일분)(+헬로키티 카드스티커)</t>
+          <t>지노마스터 질유산균 30캡슐 기획 (+보라지유 5일분) (1개월분)</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>올더베러</t>
+          <t>지노마스터</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>9,300원</t>
+          <t>27,400원</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000262970&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=8</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000244929&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=8</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0026/A00000026297012ko.jpg?l=ko</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024492930ko.jpg?l=ko</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="J9" t="n">
+        <v>25223</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>경이로운 목 넘김 — 170mg의 아주 작고 가벼운 캡슐 사이즈로 물과 함께 훅 가볍게 넘어감</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>질과 장의 이중 관리 — 질 건강 유산균뿐만 아니라 장까지 더블 케어가 가능하여 효율적임</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>한정판 캐릭터 굿즈 — 삐, 피카츄 등 포켓몬 랜덤 카드케이스가 함께 들어있어 소장 가치를 더함</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr"/>
@@ -6646,7 +6699,7 @@
     <row r="10" ht="38" customHeight="1">
       <c r="B10" t="inlineStr">
         <is>
-          <t>프로바이오틱스/유산균</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -6654,50 +6707,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>지노마스터 질유산균 30캡슐 기획 (+보라지유 5일분) (1개월분)</t>
+          <t>[한선화 PICK] 프로뉴트리션 듀얼플랜 다이어트 유산균 14포</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>지노마스터</t>
+          <t>프로뉴트리션</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>27,400원</t>
+          <t>39,800원</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000244929&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=9</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000205496&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=9</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024492930ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020549614ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I10" t="n">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="J10" t="n">
-        <v>25215</v>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>작은 캡슐 크기와 편한 목넘김 — 170mg의 작고 가벼운 캡슐 크기로 목넘김이 매우 수월하여 꾸준히 먹기 좋음</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>질과 장의 동시 더블 케어 — 식약처 인정 기능성 원료와 50억 보장균수로 질과 장을 한 번에 케어함</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>귀여운 에디션과 굿즈 — 포켓몬 에디션 패키지와 카드케이스 등 증정 굿즈가 만족스러움</t>
-        </is>
-      </c>
+        <v>497</v>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
@@ -6705,7 +6746,7 @@
     <row r="11" ht="38" customHeight="1">
       <c r="B11" t="inlineStr">
         <is>
-          <t>멀티비타민/종합비타민</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -6713,41 +6754,41 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>[9월 올영픽/김우빈PICK] 아임비타 멀티비타민 이뮨샷 12입 (+포차코 메쉬백) (12일분)</t>
+          <t>[파격특가] 콜레올로지 컷팅 젤리 레몬/키위/석류 10+2+2포 기획 외</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>아임비타</t>
+          <t>푸드올로지</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>25,900원</t>
+          <t>18,800원</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000249166&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=10</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000183645&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=10</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A000000249166123ko.jpg?l=ko</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="J11" t="n">
-        <v>10960</v>
-      </c>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0018/A00000018364587ko.jpg?l=ko</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
-          <t>꾸준히 즐겨 찾는 이뮨 비타민 — 일상적인 활력 및 피로 관리를 위해 즐겨 챙겨 마시는 멀티비타민임</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr"/>
+          <t>탁월한 디톡스 작용 — 클렌즈 제품 섭취 후 더부룩하던 뱃살이 정리되고 배변이 눈에 띄게 수월해짐</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>지속가능한 관리 — 굶는 다이어트 대신 매일 아침 공복 오일 섭취 등으로 속을 편하게 리셋함</t>
+        </is>
+      </c>
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
@@ -6869,47 +6910,47 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
+          <t>비타민C/항산화</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
           <t>프로바이오틱스/유산균</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>다이어트/체중관리</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
         <is>
           <t>비타민C/항산화</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>프로바이오틱스/유산균</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>프로바이오틱스/유산균</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
         <is>
           <t>다이어트/체중관리</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>프로바이오틱스/유산균</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>비타민C/항산화</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>프로바이오틱스/유산균</t>
-        </is>
-      </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>멀티비타민/종합비타민</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
     </row>
@@ -6926,47 +6967,47 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
+          <t>고려은단</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>올더베러</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
           <t>덴프스</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>올더베러</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>바이오코어유산균</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>고려은단</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>바이오코어유산균</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>덴프스</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>딥트3일</t>
-        </is>
-      </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>올더베러</t>
+          <t>지노마스터</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>지노마스터</t>
+          <t>프로뉴트리션</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>아임비타</t>
+          <t>푸드올로지</t>
         </is>
       </c>
     </row>
@@ -6978,52 +7019,52 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
+          <t>고려은단 비타민C1000 600정 (20개월분)</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
           <t>[9월 올영픽] 고려은단 비타민C1000 이지+비타민D 120정 (+마이멜로디 파우치) (60일분)</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>올더베러 웰니스 구미 30일분 택1</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>덴프스 덴마크 유산균이야기 우먼 2개월분(질유산균) + 철분 헤모케어 3포 증정</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>올더베러 웰니스 구미 30일분 택1</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>[9월 올영픽/산리오콜라보] CJ 바이오코어 유산균 3종 (피부/다이어트/500억) (+산리오 러기지택)</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
         <is>
           <t>[9월 올영픽] 고려은단 메가도스C 비타민C 3000mg 30포 (+헬로키티 파우치)</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>[9월 올영픽/산리오콜라보] CJ 바이오코어 유산균 3종 (피부/다이어트/500억) (+산리오 러기지택)</t>
-        </is>
-      </c>
-      <c r="H5" s="3" t="inlineStr">
+      <c r="I5" s="3" t="inlineStr">
         <is>
           <t>[덴프스] 덴마크 유산균이야기 30캡슐 1+1 기획 (+트루바이타민 3포 증정)</t>
         </is>
       </c>
-      <c r="I5" s="3" t="inlineStr">
-        <is>
-          <t>[딥트3일/남규리Pick]남규리의 바른 효소 리셋 8포</t>
-        </is>
-      </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>[산리오 에디션] 올더베러 비타민C 구미 60구미 (30일분)(+헬로키티 카드스티커)</t>
+          <t>지노마스터 질유산균 30캡슐 기획 (+보라지유 5일분) (1개월분)</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>지노마스터 질유산균 30캡슐 기획 (+보라지유 5일분) (1개월분)</t>
+          <t>[한선화 PICK] 프로뉴트리션 듀얼플랜 다이어트 유산균 14포</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>[9월 올영픽/김우빈PICK] 아임비타 멀티비타민 이뮨샷 12입 (+포차코 메쉬백) (12일분)</t>
+          <t>[파격특가] 콜레올로지 컷팅 젤리 레몬/키위/석류 10+2+2포 기획 외</t>
         </is>
       </c>
     </row>
@@ -7033,28 +7074,26 @@
           <t>평점</t>
         </is>
       </c>
-      <c r="C6" s="3" t="n">
-        <v>4.9</v>
-      </c>
+      <c r="C6" s="3" t="inlineStr"/>
       <c r="D6" s="3" t="n">
         <v>4.9</v>
       </c>
-      <c r="E6" s="3" t="inlineStr"/>
-      <c r="F6" s="3" t="n">
+      <c r="E6" s="3" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="F6" s="3" t="inlineStr"/>
+      <c r="G6" s="3" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H6" s="3" t="inlineStr"/>
+      <c r="I6" s="3" t="inlineStr"/>
+      <c r="J6" s="3" t="n">
         <v>4.9</v>
       </c>
-      <c r="G6" s="3" t="inlineStr"/>
-      <c r="H6" s="3" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="I6" s="3" t="inlineStr"/>
-      <c r="J6" s="3" t="inlineStr"/>
       <c r="K6" s="3" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="L6" s="3" t="n">
-        <v>4.9</v>
-      </c>
+        <v>4.5</v>
+      </c>
+      <c r="L6" s="3" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="B7" s="1" t="inlineStr">
@@ -7062,28 +7101,26 @@
           <t>리뷰수</t>
         </is>
       </c>
-      <c r="C7" s="3" t="n">
-        <v>15548</v>
-      </c>
+      <c r="C7" s="3" t="inlineStr"/>
       <c r="D7" s="3" t="n">
-        <v>8168</v>
-      </c>
-      <c r="E7" s="3" t="inlineStr"/>
-      <c r="F7" s="3" t="n">
-        <v>5753</v>
-      </c>
-      <c r="G7" s="3" t="inlineStr"/>
-      <c r="H7" s="3" t="n">
-        <v>24395</v>
-      </c>
+        <v>15549</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>4819</v>
+      </c>
+      <c r="F7" s="3" t="inlineStr"/>
+      <c r="G7" s="3" t="n">
+        <v>12559</v>
+      </c>
+      <c r="H7" s="3" t="inlineStr"/>
       <c r="I7" s="3" t="inlineStr"/>
-      <c r="J7" s="3" t="inlineStr"/>
+      <c r="J7" s="3" t="n">
+        <v>25223</v>
+      </c>
       <c r="K7" s="3" t="n">
-        <v>25215</v>
-      </c>
-      <c r="L7" s="3" t="n">
-        <v>10960</v>
-      </c>
+        <v>497</v>
+      </c>
+      <c r="L7" s="3" t="inlineStr"/>
     </row>
     <row r="8" ht="90" customHeight="1">
       <c r="B8" s="1" t="inlineStr">
@@ -7091,34 +7128,41 @@
           <t>긍정리뷰</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>비타민C와 D의 효율적 조합 — 비타민B 트러블 걱정 없이 면역력과 실내 비타민D 부족을 동시에 챙김
-높은 브랜드 신뢰도와 가성비 — 대한민국 1등 비타민 브랜드로서 높은 가성비와 확실한 효과를 제공함</t>
-        </is>
-      </c>
+      <c r="C8" s="3" t="inlineStr"/>
       <c r="D8" s="3" t="inlineStr"/>
-      <c r="E8" s="3" t="inlineStr"/>
-      <c r="F8" s="3" t="inlineStr"/>
-      <c r="G8" s="3" t="inlineStr"/>
-      <c r="H8" s="3" t="inlineStr">
-        <is>
-          <t>장 건강 및 면역력 관리 — 아침 공복에 물과 섭취 시 장 건강 및 면역력 케어에 우수한 효과를 보임
-1일 1캡슐과 알찬 기획 — 하루 한 알로 간편하게 섭취하며 1+1 기획으로 두 달간 경제적으로 복용 가능함</t>
-        </is>
-      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>유연한 섭취 루틴 — 아침 공복의 캡슐 오일부터 간식 형태의 콜라겐 구미까지 라이프에 맞게 다양함
+가성비 정기 세일 — 올영 세일 기간에 할인쿠폰을 중복하여 사용하면 한층 경제적으로 쟁여둠
+수분 피로 동시 케어 — 구덕하고 무거운 제형 대신 탄산수나 물에 섞는 형태로 청량하게 보충함</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>공복 건강 스타트 — 아침 기상 후 공복 상태에서 물 한 컵과 함께 편하게 습관화하기 좋음
+소장 욕구 굿즈 — 세계 1등 유산균의 메리트에 더해 공유 포토카드와 캐릭터 키링 등을 함께 줌</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>가스 없는 편안함 — 100억 유산균 보장으로 배 아픔이나 복부 가스 참 현상 없이 장이 편안함
+귀여운 산리오 콜라보 — 인기 캐릭터 산리오 디자인 패키지와 전용 러기지택 증정 혜택으로 흥미를 유발함</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr"/>
       <c r="I8" s="3" t="inlineStr"/>
-      <c r="J8" s="3" t="inlineStr"/>
-      <c r="K8" s="3" t="inlineStr">
-        <is>
-          <t>작은 캡슐 크기와 편한 목넘김 — 170mg의 작고 가벼운 캡슐 크기로 목넘김이 매우 수월하여 꾸준히 먹기 좋음
-질과 장의 동시 더블 케어 — 식약처 인정 기능성 원료와 50억 보장균수로 질과 장을 한 번에 케어함
-귀여운 에디션과 굿즈 — 포켓몬 에디션 패키지와 카드케이스 등 증정 굿즈가 만족스러움</t>
-        </is>
-      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>경이로운 목 넘김 — 170mg의 아주 작고 가벼운 캡슐 사이즈로 물과 함께 훅 가볍게 넘어감
+질과 장의 이중 관리 — 질 건강 유산균뿐만 아니라 장까지 더블 케어가 가능하여 효율적임
+한정판 캐릭터 굿즈 — 삐, 피카츄 등 포켓몬 랜덤 카드케이스가 함께 들어있어 소장 가치를 더함</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr"/>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>꾸준히 즐겨 찾는 이뮨 비타민 — 일상적인 활력 및 피로 관리를 위해 즐겨 챙겨 마시는 멀티비타민임</t>
+          <t>탁월한 디톡스 작용 — 클렌즈 제품 섭취 후 더부룩하던 뱃살이 정리되고 배변이 눈에 띄게 수월해짐
+지속가능한 관리 — 굶는 다이어트 대신 매일 아침 공복 오일 섭취 등으로 속을 편하게 리셋함</t>
         </is>
       </c>
     </row>
@@ -7132,7 +7176,11 @@
       <c r="D9" s="3" t="inlineStr"/>
       <c r="E9" s="3" t="inlineStr"/>
       <c r="F9" s="3" t="inlineStr"/>
-      <c r="G9" s="3" t="inlineStr"/>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>다소 큼직한 제형 — 기존에 평범하게 복용하던 타 영양제에 비해 알약의 물리적 두께가 있는 편임</t>
+        </is>
+      </c>
       <c r="H9" s="3" t="inlineStr"/>
       <c r="I9" s="3" t="inlineStr"/>
       <c r="J9" s="3" t="inlineStr"/>
@@ -7147,52 +7195,52 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
+          <t>42,900원</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
           <t>10,900원</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>9,200원</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
         <is>
           <t>31,400원</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t>9,200원</t>
-        </is>
-      </c>
-      <c r="F10" s="3" t="inlineStr">
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>12,900원</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
         <is>
           <t>9,900원</t>
         </is>
       </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t>12,900원</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="inlineStr">
+      <c r="I10" s="3" t="inlineStr">
         <is>
           <t>30,400원</t>
         </is>
       </c>
-      <c r="I10" s="3" t="inlineStr">
-        <is>
-          <t>16,000원</t>
-        </is>
-      </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>9,300원</t>
+          <t>27,400원</t>
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>27,400원</t>
+          <t>39,800원</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>25,900원</t>
+          <t>18,800원</t>
         </is>
       </c>
     </row>
@@ -7280,7 +7328,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7318,23 +7366,23 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C2" t="n">
-        <v>27.5</v>
+        <v>25</v>
       </c>
       <c r="D2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F2" t="n">
         <v>3</v>
-      </c>
-      <c r="E2" t="n">
-        <v>6</v>
-      </c>
-      <c r="F2" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -7344,10 +7392,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C3" t="n">
-        <v>25</v>
+        <v>22.5</v>
       </c>
       <c r="D3" t="n">
         <v>9</v>
@@ -7356,26 +7404,26 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C4" t="n">
-        <v>15</v>
+        <v>17.5</v>
       </c>
       <c r="D4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F4" t="n">
         <v>1</v>
@@ -7384,20 +7432,20 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>비타민C/항산화</t>
+          <t>프로바이오틱스/유산균</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C5" t="n">
-        <v>12.5</v>
+        <v>7.5</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
         <v>3</v>
@@ -7406,7 +7454,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>프로바이오틱스/유산균</t>
+          <t>비타민C/항산화</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -7428,7 +7476,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>피부/미용</t>
+          <t>비타민D</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -7438,10 +7486,10 @@
         <v>5</v>
       </c>
       <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
         <v>2</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -7454,16 +7502,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C8" t="n">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="D8" t="n">
         <v>1</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -7472,20 +7520,20 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>혈행</t>
+          <t>피부/미용</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C9" t="n">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="D9" t="n">
+        <v>2</v>
+      </c>
+      <c r="E9" t="n">
         <v>0</v>
-      </c>
-      <c r="E9" t="n">
-        <v>1</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
@@ -7494,7 +7542,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>비타민D</t>
+          <t>루테인/눈건강</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -7510,6 +7558,28 @@
         <v>1</v>
       </c>
       <c r="F10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>혈행</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" t="n">
         <v>0</v>
       </c>
     </row>
